--- a/analysis/trigger_analysis.xlsx
+++ b/analysis/trigger_analysis.xlsx
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.7445901770077653</v>
+        <v>0.7759283463087604</v>
       </c>
     </row>
     <row r="10">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>-666952604</v>
+        <v>-1354281610</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>11101345598</v>
@@ -642,7 +642,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12 / 20</t>
+          <t>11 / 20</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -654,7 +654,7 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>⚠ SpaceX (SPCX) IPO disclosure — read before the ramp number</t>
+          <t>⚠ IPO-reclassification disclosure — read before the ramp number</t>
         </is>
       </c>
       <c r="B14" s="9" t="n"/>
@@ -664,35 +664,35 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>SPCX is a $4.67B position (32.6% of the book) labeled IPO_RECLASSIFICATION — it entered the 13F because SpaceX IPO'd in Q2 2026, converting a pre-existing private holding</t>
+          <t>2 positions labeled IPO_RECLASSIFICATION (SPCX $4.67B + CBRS $0.69B) entered the 13F at their 2026 IPOs — pre-existing private crossover holdings becoming reportable, NOT market</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>into a reportable security. It was NOT freshly bought in the market, so it is excluded from every net-buying total on these sheets (Holdings, Baskets, Flows).</t>
+          <t>purchases ($5.36B combined). They are excluded from every net-buying total and from the thesis-book denominator on these sheets (Holdings, Baskets, Flows).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>Net trading AS-FILED (SPCX counted as a buy):   $4.00B</t>
+          <t>Net trading AS-FILED (reclassifications counted as buys):   $4.00B</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>Net trading EX-SpaceX (true market flow):   $-0.67B  → net SELLER once SPCX is stripped.</t>
+          <t>Net trading EX-RECLASS (true market flow):   $-1.35B  → net SELLER once SPCX + CBRS are stripped.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>Ex-SpaceX, the AI book was self-funded (sold Astera −$1.04B to fund Cerebras/CoreWeave/Amphenol); genuinely new capital went to SPCX + the QQQ hedge, not the AI names.</t>
+          <t>The AI book was self-funded (sold Astera −$1.04B to fund CoreWeave/Amphenol/etc.); genuinely new market capital went to the QQQ hedge, not the AI names.</t>
         </is>
       </c>
     </row>
@@ -4308,7 +4308,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="BV6" s="5" t="n">
-        <v>0.04234273457266797</v>
+        <v>0.04736848588717928</v>
       </c>
     </row>
     <row r="7">
@@ -4485,7 +4485,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="BV7" s="5" t="n">
-        <v>0.01430751182133913</v>
+        <v>0.01600570153603687</v>
       </c>
     </row>
     <row r="8">
@@ -4821,7 +4821,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="AI10" s="5" t="n">
-        <v>0.09123707785077395</v>
+        <v>0.1020662051749379</v>
       </c>
     </row>
     <row r="11">
@@ -4914,7 +4914,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>0.1081465804226605</v>
+        <v>0.1209827334062689</v>
       </c>
     </row>
     <row r="12">
@@ -5079,7 +5079,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="Z13" s="5" t="n">
-        <v>0.01476462151073128</v>
+        <v>0.01651706656924476</v>
       </c>
     </row>
     <row r="14">
@@ -5145,7 +5145,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>0.04520179943228864</v>
+        <v>0.05056689937700833</v>
       </c>
     </row>
     <row r="15">
@@ -5202,7 +5202,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>0.03264913736443333</v>
+        <v>0.03652433453067583</v>
       </c>
     </row>
     <row r="16">
@@ -5223,7 +5223,7 @@
         <v>0.0192</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.01360846544755759</v>
+        <v>0.0152236838268564</v>
       </c>
     </row>
   </sheetData>
@@ -5237,7 +5237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX40"/>
+  <dimension ref="A1:BX39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6201,7 +6201,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="BV4" s="5" t="n">
-        <v>0.01430751182133913</v>
+        <v>0.01600570153603687</v>
       </c>
     </row>
     <row r="5">
@@ -6570,7 +6570,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="BJ6" s="5" t="n">
-        <v>0.03567379820664982</v>
+        <v>0.03990799895065209</v>
       </c>
     </row>
     <row r="7">
@@ -6702,7 +6702,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="BD7" s="5" t="n">
-        <v>0.01430751182133913</v>
+        <v>0.01600570153603687</v>
       </c>
     </row>
     <row r="8">
@@ -6837,7 +6837,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="AX8" s="5" t="n">
-        <v>0.03502159938602322</v>
+        <v>0.03917838923266218</v>
       </c>
     </row>
     <row r="9">
@@ -7449,7 +7449,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="AR13" s="5" t="n">
-        <v>0.03858653799729827</v>
+        <v>0.0431664581658823</v>
       </c>
     </row>
     <row r="14">
@@ -7650,7 +7650,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="AI15" s="5" t="n">
-        <v>0.02693692890472359</v>
+        <v>0.03013413161772924</v>
       </c>
     </row>
     <row r="16">
@@ -7743,7 +7743,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="AI16" s="5" t="n">
-        <v>0.03502159938602322</v>
+        <v>0.03917838923266218</v>
       </c>
     </row>
     <row r="17">
@@ -7851,7 +7851,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="AI17" s="5" t="n">
-        <v>0.05213821328823285</v>
+        <v>0.05832661128883693</v>
       </c>
     </row>
     <row r="18">
@@ -8025,7 +8025,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="AF19" s="5" t="n">
-        <v>0.03567379820664982</v>
+        <v>0.03990799895065209</v>
       </c>
     </row>
     <row r="20">
@@ -8187,7 +8187,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="AC21" s="5" t="n">
-        <v>0.09072549578446804</v>
+        <v>0.1014939023198552</v>
       </c>
     </row>
     <row r="22">
@@ -8280,7 +8280,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>0.1267516543935302</v>
+        <v>0.1417960840959038</v>
       </c>
     </row>
     <row r="23">
@@ -8373,7 +8373,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="AC23" s="5" t="n">
-        <v>0.02693692890472359</v>
+        <v>0.03013413161772924</v>
       </c>
     </row>
     <row r="24">
@@ -8736,7 +8736,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>0.04520179943228864</v>
+        <v>0.05056689937700833</v>
       </c>
     </row>
     <row r="30">
@@ -8838,7 +8838,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>0.03502159938602322</v>
+        <v>0.03917838923266218</v>
       </c>
     </row>
     <row r="32">
@@ -8895,7 +8895,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="Q32" s="5" t="n">
-        <v>0.03858653799729827</v>
+        <v>0.0431664581658823</v>
       </c>
     </row>
     <row r="33">
@@ -8952,7 +8952,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>0.03264913736443333</v>
+        <v>0.03652433453067583</v>
       </c>
     </row>
     <row r="34">
@@ -9090,7 +9090,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>0.05213821328823285</v>
+        <v>0.05832661128883693</v>
       </c>
     </row>
     <row r="37">
@@ -9129,7 +9129,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>0.03909886456254109</v>
+        <v>0.04373959388610092</v>
       </c>
     </row>
     <row r="38">
@@ -9168,7 +9168,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>0.01430751182133913</v>
+        <v>0.01600570153603687</v>
       </c>
     </row>
     <row r="39">
@@ -9177,34 +9177,16 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CBRS</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AI/Datacenter Chips</t>
+          <t>AI/Hyperscaler</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>0.1061</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="27" t="n">
-        <v>46248</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>AI/Hyperscaler</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>0.035</v>
+        <v>0.0392</v>
       </c>
     </row>
   </sheetData>
@@ -10201,7 +10183,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="CF3" s="5" t="n">
-        <v>0.1267516543935302</v>
+        <v>0.1417960840959038</v>
       </c>
     </row>
     <row r="4">
@@ -10425,7 +10407,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="BW4" s="5" t="n">
-        <v>0.1446855871938777</v>
+        <v>0.0431664581658823</v>
       </c>
     </row>
     <row r="5">
@@ -10649,7 +10631,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="BT5" s="5" t="n">
-        <v>0.09763232649739663</v>
+        <v>0.1092205198010435</v>
       </c>
     </row>
     <row r="6">
@@ -10843,7 +10825,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="BN6" s="5" t="n">
-        <v>0.1267516543935302</v>
+        <v>0.1417960840959038</v>
       </c>
     </row>
     <row r="7">
@@ -11007,7 +10989,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="BN7" s="5" t="n">
-        <v>0.01430751182133913</v>
+        <v>0.01600570153603687</v>
       </c>
     </row>
     <row r="8">
@@ -11186,7 +11168,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="BE8" s="5" t="n">
-        <v>0.1446855871938777</v>
+        <v>0.0431664581658823</v>
       </c>
     </row>
     <row r="9">
@@ -11466,7 +11448,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="AP10" s="5" t="n">
-        <v>0.09123707785077395</v>
+        <v>0.1020662051749379</v>
       </c>
     </row>
     <row r="11">
@@ -11600,7 +11582,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="AP11" s="5" t="n">
-        <v>0.01326268050050824</v>
+        <v>0.01483685691192967</v>
       </c>
     </row>
     <row r="12">
@@ -11725,7 +11707,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="AM12" s="5" t="n">
-        <v>0.1267516543935302</v>
+        <v>0.1417960840959038</v>
       </c>
     </row>
     <row r="13">
@@ -11838,7 +11820,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="AM13" s="5" t="n">
-        <v>0.1081465804226605</v>
+        <v>0.1209827334062689</v>
       </c>
     </row>
     <row r="14">
@@ -12052,7 +12034,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="AJ15" s="5" t="n">
-        <v>0.01326268050050824</v>
+        <v>0.01483685691192967</v>
       </c>
     </row>
     <row r="16">
@@ -12236,7 +12218,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="AA17" s="5" t="n">
-        <v>0.04520179943228864</v>
+        <v>0.05056689937700833</v>
       </c>
     </row>
     <row r="18">
@@ -12372,7 +12354,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>0.1081465804226605</v>
+        <v>0.1209827334062689</v>
       </c>
     </row>
   </sheetData>
@@ -13506,7 +13488,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="CF4" s="5" t="n">
-        <v>0.04234273457266797</v>
+        <v>0.04736848588717928</v>
       </c>
     </row>
     <row r="5">
@@ -13697,7 +13679,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="CF5" s="5" t="n">
-        <v>0.01430751182133913</v>
+        <v>0.01600570153603687</v>
       </c>
     </row>
     <row r="6">
@@ -13921,7 +13903,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="BW6" s="5" t="n">
-        <v>0.1446855871938777</v>
+        <v>0.0431664581658823</v>
       </c>
     </row>
     <row r="7">
@@ -14145,7 +14127,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="BT7" s="5" t="n">
-        <v>0.09763232649739663</v>
+        <v>0.1092205198010435</v>
       </c>
     </row>
     <row r="8">
@@ -14339,7 +14321,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="BN8" s="5" t="n">
-        <v>0.1267516543935302</v>
+        <v>0.1417960840959038</v>
       </c>
     </row>
     <row r="9">
@@ -14503,7 +14485,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="BN9" s="5" t="n">
-        <v>0.01430751182133913</v>
+        <v>0.01600570153603687</v>
       </c>
     </row>
     <row r="10">
@@ -14691,7 +14673,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="BH10" s="5" t="n">
-        <v>0.01326268050050824</v>
+        <v>0.01483685691192967</v>
       </c>
     </row>
     <row r="11">
@@ -14870,7 +14852,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="BE11" s="5" t="n">
-        <v>0.1446855871938777</v>
+        <v>0.0431664581658823</v>
       </c>
     </row>
     <row r="12">
@@ -15204,7 +15186,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="BB13" s="5" t="n">
-        <v>0.01326268050050824</v>
+        <v>0.01483685691192967</v>
       </c>
     </row>
     <row r="14">
@@ -15347,7 +15329,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="AS14" s="5" t="n">
-        <v>0.09123707785077395</v>
+        <v>0.1020662051749379</v>
       </c>
     </row>
     <row r="15">
@@ -15481,7 +15463,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="AP15" s="5" t="n">
-        <v>0.01326268050050824</v>
+        <v>0.01483685691192967</v>
       </c>
     </row>
     <row r="16">
@@ -15722,7 +15704,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="AM17" s="5" t="n">
-        <v>0.1267516543935302</v>
+        <v>0.1417960840959038</v>
       </c>
     </row>
     <row r="18">
@@ -15835,7 +15817,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="AM18" s="5" t="n">
-        <v>0.1081465804226605</v>
+        <v>0.1209827334062689</v>
       </c>
     </row>
     <row r="19">
@@ -16049,7 +16031,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="AJ20" s="5" t="n">
-        <v>0.01326268050050824</v>
+        <v>0.01483685691192967</v>
       </c>
     </row>
     <row r="21">
@@ -16242,7 +16224,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="AD22" s="5" t="n">
-        <v>0.04520179943228864</v>
+        <v>0.05056689937700833</v>
       </c>
     </row>
     <row r="23">
@@ -16319,7 +16301,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="AA23" s="5" t="n">
-        <v>0.03264913736443333</v>
+        <v>0.03652433453067583</v>
       </c>
     </row>
     <row r="24">
@@ -16408,7 +16390,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="AA24" s="5" t="n">
-        <v>0.1267516543935302</v>
+        <v>0.1417960840959038</v>
       </c>
     </row>
     <row r="25">
@@ -16497,7 +16479,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="AA25" s="5" t="n">
-        <v>0.01476462151073128</v>
+        <v>0.01651706656924476</v>
       </c>
     </row>
     <row r="26">
@@ -16651,7 +16633,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="X27" s="5" t="n">
-        <v>0.01326268050050824</v>
+        <v>0.01483685691192967</v>
       </c>
     </row>
     <row r="28">
@@ -16722,7 +16704,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="U28" s="5" t="n">
-        <v>0.1267516543935302</v>
+        <v>0.1417960840959038</v>
       </c>
     </row>
     <row r="29">
@@ -16793,7 +16775,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="U29" s="5" t="n">
-        <v>0.01430751182133913</v>
+        <v>0.01600570153603687</v>
       </c>
     </row>
     <row r="30">
@@ -16855,7 +16837,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="R30" s="5" t="n">
-        <v>0.1081465804226605</v>
+        <v>0.1209827334062689</v>
       </c>
     </row>
     <row r="31">
@@ -16908,7 +16890,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>0.04234273457266797</v>
+        <v>0.04736848588717928</v>
       </c>
     </row>
     <row r="32">
@@ -16961,7 +16943,7 @@
         <v>0.3402000000000001</v>
       </c>
       <c r="O32" s="5" t="n">
-        <v>0.01476462151073128</v>
+        <v>0.01651706656924476</v>
       </c>
     </row>
   </sheetData>
@@ -21216,10 +21198,10 @@
         <v>0.06258771818496679</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.1267516543935302</v>
+        <v>0.1417960840959038</v>
       </c>
       <c r="G3" s="19" t="n">
-        <v>0.06416393620856338</v>
+        <v>0.07920836591093698</v>
       </c>
       <c r="H3" s="5" t="n">
         <v>0.05727913898289666</v>
@@ -21283,31 +21265,19 @@
         <v>687329006</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.1060990491965794</v>
-      </c>
-      <c r="G4" s="19" t="n">
-        <v>0.1060990491965794</v>
+        <v>0.06165331702579317</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>0.0479462158814573</v>
       </c>
-      <c r="K4" s="7" t="n">
-        <v>687329006</v>
-      </c>
-      <c r="L4" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="7" t="n">
-        <v>687329006</v>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>NEW — buy</t>
+          <t>IPO reclass — not a buy</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>IPO_RECLASSIFICATION</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -21342,10 +21312,10 @@
         <v>0.0898707311055834</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.09072549578446804</v>
+        <v>0.1014939023198552</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>0.0008547646788846385</v>
+        <v>0.01162317121427178</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>0.04099889904550236</v>
@@ -21412,10 +21382,10 @@
         <v>0.06401400899378704</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.05213821328823285</v>
+        <v>0.05832661128883693</v>
       </c>
       <c r="G6" s="21" t="n">
-        <v>-0.01187579570555418</v>
+        <v>-0.005687397704950108</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>0.02356128588258519</v>
@@ -21478,10 +21448,10 @@
         <v>0.02495544981159786</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.04740666923237497</v>
+        <v>0.05303346997199945</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>0.02245121942077712</v>
+        <v>0.0280780201604016</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>0.02142309864648221</v>
@@ -21540,10 +21510,10 @@
         <v>0.02194260634603171</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.04616400541827215</v>
+        <v>0.05164331168546231</v>
       </c>
       <c r="G8" s="19" t="n">
-        <v>0.02422139907224045</v>
+        <v>0.0297007053394306</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>0.02086153821827651</v>
@@ -21606,10 +21576,10 @@
         <v>0.06620107137492426</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.04520179943228864</v>
+        <v>0.05056689937700833</v>
       </c>
       <c r="G9" s="21" t="n">
-        <v>-0.02099927194263561</v>
+        <v>-0.01563417199791593</v>
       </c>
       <c r="H9" s="5" t="n">
         <v>0.02042671682943523</v>
@@ -21676,10 +21646,10 @@
         <v>0.03662856119767579</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.03909886456254109</v>
+        <v>0.04373959388610092</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>0.002470303364865298</v>
+        <v>0.007111032688425127</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>0.01766879736652619</v>
@@ -21746,10 +21716,10 @@
         <v>0.0530503338279851</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.03858653799729827</v>
+        <v>0.0431664581658823</v>
       </c>
       <c r="G11" s="21" t="n">
-        <v>-0.01446379583068682</v>
+        <v>-0.00988387566210279</v>
       </c>
       <c r="H11" s="5" t="n">
         <v>0.0174372767234578</v>
@@ -21816,10 +21786,10 @@
         <v>0.04838333870796754</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.03567379820664982</v>
+        <v>0.03990799895065209</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>-0.01270954050131771</v>
+        <v>-0.008475339757315438</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>0.01612100808706135</v>
@@ -21883,10 +21853,10 @@
         <v>226876313</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.03502159938602323</v>
+        <v>0.03917838923266219</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>0.03502159938602323</v>
+        <v>0.03917838923266219</v>
       </c>
       <c r="H13" s="5" t="n">
         <v>0.0158262790985531</v>
@@ -21950,10 +21920,10 @@
         <v>0.01529770979910688</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.03264913736443333</v>
+        <v>0.03652433453067583</v>
       </c>
       <c r="G14" s="19" t="n">
-        <v>0.01735142756532645</v>
+        <v>0.02122662473156895</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>0.01475416226886359</v>
@@ -22020,10 +21990,10 @@
         <v>0.03888307006753539</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.02693692890472359</v>
+        <v>0.03013413161772924</v>
       </c>
       <c r="G15" s="21" t="n">
-        <v>-0.01194614116281181</v>
+        <v>-0.008748938449806154</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>0.01217281227522049</v>
@@ -22090,10 +22060,10 @@
         <v>0.02824972229405384</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.02294275277335922</v>
+        <v>0.02566587802903524</v>
       </c>
       <c r="G16" s="21" t="n">
-        <v>-0.005306969520694618</v>
+        <v>-0.0025838442650186</v>
       </c>
       <c r="H16" s="5" t="n">
         <v>0.0103678419902546</v>
@@ -22153,10 +22123,10 @@
         <v>112856966</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.01742108463819246</v>
+        <v>0.01948883108641369</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>0.01742108463819246</v>
+        <v>0.01948883108641369</v>
       </c>
       <c r="H17" s="5" t="n">
         <v>0.007872597269032302</v>
@@ -22212,10 +22182,10 @@
         <v>0.01910597190573455</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.01661577389199343</v>
+        <v>0.0185879362551964</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>-0.002490198013741114</v>
+        <v>-0.000518035650538149</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>0.007508676921194155</v>
@@ -22282,10 +22252,10 @@
         <v>0.01333641309226726</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.01602567196331084</v>
+        <v>0.01792779384439325</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>0.002689258871043576</v>
+        <v>0.004591380752125989</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>0.007242009550667027</v>
@@ -22345,10 +22315,10 @@
         <v>102982850</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.01589687380158951</v>
+        <v>0.01778370834856112</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>0.01589687380158951</v>
+        <v>0.01778370834856112</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>0.007183805593951226</v>
@@ -22408,10 +22378,10 @@
         <v>0.00702901746323455</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.01430751182133913</v>
+        <v>0.01600570153603687</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>0.007278494358104575</v>
+        <v>0.008976684072802318</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>0.006465572082945151</v>
@@ -22478,10 +22448,10 @@
         <v>0.01014938146727072</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.01377145298249926</v>
+        <v>0.01540601670702078</v>
       </c>
       <c r="G22" s="19" t="n">
-        <v>0.003622071515228533</v>
+        <v>0.005256635239750054</v>
       </c>
       <c r="H22" s="5" t="n">
         <v>0.006223326813012907</v>
@@ -22541,10 +22511,10 @@
         <v>87867021</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.0135635296960476</v>
+        <v>0.01517341455320857</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>0.0135635296960476</v>
+        <v>0.01517341455320857</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>0.006129366171004491</v>
@@ -22600,10 +22570,10 @@
         <v>0.01818548810253011</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.01326268050050824</v>
+        <v>0.01483685691192967</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>-0.004922807602021877</v>
+        <v>-0.003348631190600439</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>0.005993412262026784</v>
@@ -22670,10 +22640,10 @@
         <v>0.02186101087294426</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.01313339254091695</v>
+        <v>0.01469222348305248</v>
       </c>
       <c r="G25" s="21" t="n">
-        <v>-0.008727618332027303</v>
+        <v>-0.007168787389891778</v>
       </c>
       <c r="H25" s="5" t="n">
         <v>0.005934986965397107</v>
@@ -22736,10 +22706,10 @@
         <v>0.02622016393066834</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.01203879957799664</v>
+        <v>0.01346771089926284</v>
       </c>
       <c r="G26" s="21" t="n">
-        <v>-0.0141813643526717</v>
+        <v>-0.01275245303140551</v>
       </c>
       <c r="H26" s="5" t="n">
         <v>0.00544033983236518</v>
@@ -22802,10 +22772,10 @@
         <v>0.005337294757905393</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.01195550769817527</v>
+        <v>0.0133745329249621</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>0.006618212940269881</v>
+        <v>0.008037238167056706</v>
       </c>
       <c r="H27" s="5" t="n">
         <v>0.005402700188265369</v>
@@ -22865,10 +22835,10 @@
         <v>74869487</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.01155717467936405</v>
+        <v>0.01292892089327872</v>
       </c>
       <c r="G28" s="19" t="n">
-        <v>0.01155717467936405</v>
+        <v>0.01292892089327872</v>
       </c>
       <c r="H28" s="5" t="n">
         <v>0.005222693288512199</v>
@@ -22928,10 +22898,10 @@
         <v>0.01005539476111724</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.01099139886367521</v>
+        <v>0.01229599191476008</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>0.0009360041025579657</v>
+        <v>0.00224059715364284</v>
       </c>
       <c r="H29" s="5" t="n">
         <v>0.004967018901183199</v>
@@ -22994,10 +22964,10 @@
         <v>0.009905337859333493</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.01076973839095078</v>
+        <v>0.01204802207814093</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>0.0008644005316172853</v>
+        <v>0.002142684218807435</v>
       </c>
       <c r="H30" s="5" t="n">
         <v>0.004866850417505834</v>
@@ -23056,10 +23026,10 @@
         <v>0.01427220699455487</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.01021432149920124</v>
+        <v>0.01142668154678749</v>
       </c>
       <c r="G31" s="21" t="n">
-        <v>-0.004057885495353626</v>
+        <v>-0.002845525447767374</v>
       </c>
       <c r="H31" s="5" t="n">
         <v>0.004615857233328555</v>
@@ -23118,10 +23088,10 @@
         <v>0.006038267947741215</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.007423047103738744</v>
+        <v>0.008304104718836079</v>
       </c>
       <c r="G32" s="19" t="n">
-        <v>0.001384779155997529</v>
+        <v>0.002265836771094864</v>
       </c>
       <c r="H32" s="5" t="n">
         <v>0.003354478872611409</v>
@@ -23185,10 +23155,10 @@
         <v>46617763</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.007196117560578376</v>
+        <v>0.00805024041434417</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>0.007196117560578376</v>
+        <v>0.00805024041434417</v>
       </c>
       <c r="H33" s="5" t="n">
         <v>0.003251929293245356</v>
@@ -23241,10 +23211,10 @@
         <v>38331325</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.005916987500080966</v>
+        <v>0.006619287623268433</v>
       </c>
       <c r="G34" s="19" t="n">
-        <v>0.005916987500080966</v>
+        <v>0.006619287623268433</v>
       </c>
       <c r="H34" s="5" t="n">
         <v>0.002673889749201566</v>
@@ -23304,10 +23274,10 @@
         <v>0.008317042556012124</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.005413191568209599</v>
+        <v>0.006055695055860864</v>
       </c>
       <c r="G35" s="21" t="n">
-        <v>-0.002903850987802524</v>
+        <v>-0.002261347500151259</v>
       </c>
       <c r="H35" s="5" t="n">
         <v>0.002446224103820049</v>
@@ -23370,10 +23340,10 @@
         <v>0.004861492798407416</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.005176089881892354</v>
-      </c>
-      <c r="G36" s="18" t="n">
-        <v>0.0003145970834849382</v>
+        <v>0.00579045125440373</v>
+      </c>
+      <c r="G36" s="19" t="n">
+        <v>0.0009289584559963143</v>
       </c>
       <c r="H36" s="5" t="n">
         <v>0.002339077727635646</v>
@@ -23436,10 +23406,10 @@
         <v>0.004865792528508127</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.004784658335809801</v>
+        <v>0.005352559846266461</v>
       </c>
       <c r="G37" s="18" t="n">
-        <v>-8.113419269832556e-05</v>
+        <v>0.0004867673177583348</v>
       </c>
       <c r="H37" s="5" t="n">
         <v>0.002162189607021915</v>
@@ -23499,10 +23469,10 @@
         <v>28335308</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.004373959503015985</v>
+        <v>0.004893114275227872</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>0.004373959503015985</v>
+        <v>0.004893114275227872</v>
       </c>
       <c r="H38" s="5" t="n">
         <v>0.001976594589455729</v>
@@ -23558,10 +23528,10 @@
         <v>0.003526462049512132</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.003273250935931758</v>
+        <v>0.00366176021290706</v>
       </c>
       <c r="G39" s="18" t="n">
-        <v>-0.0002532111135803744</v>
+        <v>0.0001352981633949285</v>
       </c>
       <c r="H39" s="5" t="n">
         <v>0.001479183811700227</v>
@@ -23624,10 +23594,10 @@
         <v>0.00192966083782563</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.002783845614343103</v>
+        <v>0.003114266308634125</v>
       </c>
       <c r="G40" s="19" t="n">
-        <v>0.0008541847765174734</v>
+        <v>0.001184605470808496</v>
       </c>
       <c r="H40" s="5" t="n">
         <v>0.001258021290639857</v>
@@ -23686,10 +23656,10 @@
         <v>0.00159426361812715</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.002733698987731871</v>
+        <v>0.003058167669779159</v>
       </c>
       <c r="G41" s="19" t="n">
-        <v>0.001139435369604721</v>
+        <v>0.001463904051652009</v>
       </c>
       <c r="H41" s="5" t="n">
         <v>0.001235360003819329</v>
@@ -23741,10 +23711,10 @@
         <v>13790927</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.002128826558266094</v>
+        <v>0.002381501615310675</v>
       </c>
       <c r="G42" s="19" t="n">
-        <v>0.002128826558266094</v>
+        <v>0.002381501615310675</v>
       </c>
       <c r="H42" s="5" t="n">
         <v>0.0009620178362549977</v>
@@ -23797,10 +23767,10 @@
         <v>0.00105917951661963</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.0006589494794507658</v>
+        <v>0.0007371616272009947</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>-0.0004002300371688646</v>
+        <v>-0.0003220178894186357</v>
       </c>
       <c r="H43" s="5" t="n">
         <v>0.000297779614765284</v>
@@ -23859,10 +23829,10 @@
         <v>0.0006198956625919947</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.0006444909488835318</v>
+        <v>0.0007209869821754592</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>2.459528629153711e-05</v>
+        <v>0.0001010913195834644</v>
       </c>
       <c r="H44" s="5" t="n">
         <v>0.000291245797232001</v>
@@ -23918,10 +23888,10 @@
         <v>3257584</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.000502854618473631</v>
+        <v>0.0005625395274741292</v>
       </c>
       <c r="G45" s="19" t="n">
-        <v>0.000502854618473631</v>
+        <v>0.0005625395274741292</v>
       </c>
       <c r="H45" s="5" t="n">
         <v>0.0002272402653642427</v>
@@ -23974,10 +23944,10 @@
         <v>291102</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>4.493575150998744e-05</v>
+        <v>5.026927364782426e-05</v>
       </c>
       <c r="G46" s="18" t="n">
-        <v>4.493575150998744e-05</v>
+        <v>5.026927364782426e-05</v>
       </c>
       <c r="H46" s="5" t="n">
         <v>2.03064896340545e-05</v>
@@ -24033,10 +24003,10 @@
         <v>5.835831762618304e-05</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>2.367716554801899e-05</v>
+        <v>2.648745985418006e-05</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>-3.468115207816405e-05</v>
+        <v>-3.187085777200297e-05</v>
       </c>
       <c r="H47" s="5" t="n">
         <v>1.069972350763461e-05</v>
@@ -24089,7 +24059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -24115,7 +24085,7 @@
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>4823591070</v>
+        <v>4136262064</v>
       </c>
     </row>
     <row r="4">
@@ -24125,7 +24095,7 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.7445901770077653</v>
+        <v>0.7142750292829674</v>
       </c>
     </row>
     <row r="5">
@@ -24135,7 +24105,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>-215168937</v>
+        <v>-902497943</v>
       </c>
     </row>
     <row r="6">
@@ -24155,7 +24125,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1340152998</v>
+        <v>652823992</v>
       </c>
     </row>
     <row r="8">
@@ -24219,7 +24189,7 @@
         <v>0.6250289812138469</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.7445901770077651</v>
+        <v>0.7142750292829674</v>
       </c>
     </row>
     <row r="15">
@@ -24285,7 +24255,7 @@
         <v>821120352</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.1267516543935302</v>
+        <v>0.1417960840959038</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>620849808</v>
@@ -24302,199 +24272,199 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CBRS</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CEREBRAS SYSTEMS INC</t>
+          <t>ASTERA LABS INC</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>687329006</v>
+        <v>587736321</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.1060990491965794</v>
-      </c>
-      <c r="E18" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>687329006</v>
+        <v>0.1014939023198552</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>1256852182</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>-1038006116</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>AI/Datacenter Chips</t>
+          <t>AI/Datacenter Networking</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>CIEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ASTERA LABS INC</t>
+          <t>CIENA CORP</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>587736321</v>
+        <v>337760862</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0.09072549578446804</v>
+        <v>0.05832661128883693</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>1256852182</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>-1038006116</v>
+        <v>69257660</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>5746420</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>AI/Datacenter Networking</t>
+          <t>AI/Datacenter Optical</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CIEN</t>
+          <t>U</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CIENA CORP</t>
+          <t>UNITY SOFTWARE INC</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>337760862</v>
+        <v>292825507</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0.05213821328823285</v>
+        <v>0.05056689937700833</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>69257660</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>5746420</v>
+        <v>82238538</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-61146996</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>AI/Datacenter Optical</t>
+          <t>AI/World Models</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>COHR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UNITY SOFTWARE INC</t>
+          <t>COHERENT CORP</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>292825507</v>
+        <v>253289581</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0.04520179943228864</v>
+        <v>0.04373959388610092</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>82238538</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>-61146996</v>
+        <v>98624905</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>4316291</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>AI/World Models</t>
+          <t>AI/Datacenter Optical</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COHR</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>COHERENT CORP</t>
+          <t>NVIDIA CORPORATION</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>253289581</v>
+        <v>249970636</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>0.03909886456254109</v>
+        <v>0.0431664581658823</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>98624905</v>
+        <v>32076328</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>4316291</v>
+        <v>139863</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AI/Datacenter Optical</t>
+          <t>AI/Datacenter Chips</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NVIDIA CORPORATION</t>
+          <t>AMAZON COM INC</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>249970636</v>
+        <v>231101376</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0.03858653799729827</v>
+        <v>0.03990799895065209</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>32076328</v>
+        <v>28673550</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>139863</v>
+        <v>3829885</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>AI/Datacenter Chips</t>
+          <t>AI/Hyperscaler</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AMAZON COM INC</t>
+          <t>META PLATFORMS INC</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>231101376</v>
+        <v>226876313</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0.03567379820664982</v>
-      </c>
-      <c r="E24" s="7" t="n">
-        <v>28673550</v>
+        <v>0.03917838923266219</v>
+      </c>
+      <c r="E24" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>3829885</v>
+        <v>226876313</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -24505,315 +24475,315 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>META PLATFORMS INC</t>
+          <t>COREWEAVE INC</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>226876313</v>
+        <v>211507071</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>0.03502159938602323</v>
-      </c>
-      <c r="E25" s="20" t="n">
-        <v>0</v>
+        <v>0.03652433453067583</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>17888508</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>226876313</v>
+        <v>130826417</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>AI/Hyperscaler</t>
+          <t>AI/Datacenter Compute</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>COREWEAVE INC</t>
+          <t>ALPHABET INC</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>211507071</v>
+        <v>174502342</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>0.03264913736443333</v>
+        <v>0.03013413161772924</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>17888508</v>
-      </c>
-      <c r="F26" s="7" t="n">
-        <v>130826417</v>
+        <v>38746156</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-23846228</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>AI/Datacenter Compute</t>
+          <t>AI/Hyperscaler</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ALPHABET INC</t>
+          <t>AMPHENOL CORP</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>174502342</v>
+        <v>112856966</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0.02693692890472359</v>
-      </c>
-      <c r="E27" s="7" t="n">
-        <v>38746156</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>-23846228</v>
+        <v>0.01948883108641369</v>
+      </c>
+      <c r="E27" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>112856966</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>AI/Hyperscaler</t>
+          <t>AI/Datacenter Networking</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>AKAM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AMPHENOL CORP</t>
+          <t>AKAMAI TECHNOLOGIES INC</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>112856966</v>
+        <v>107640016</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>0.01742108463819246</v>
-      </c>
-      <c r="E28" s="20" t="n">
-        <v>0</v>
+        <v>0.0185879362551964</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>2294332</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>112856966</v>
+        <v>26921855</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>AI/Datacenter Networking</t>
+          <t>AI/Edge Computing</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AKAM</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AKAMAI TECHNOLOGIES INC</t>
+          <t>INTEL CORP</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>107640016</v>
+        <v>92686673</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>0.01661577389199343</v>
+        <v>0.01600570153603687</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>2294332</v>
+        <v>62437136</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>26921855</v>
+        <v>1397696</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>AI/Edge Computing</t>
+          <t>Semiconductor Manufacturing</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>INTEL CORP</t>
+          <t>SEMTECH CORP</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>92686673</v>
+        <v>89213986</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>0.01430751182133913</v>
+        <v>0.01540601670702078</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>62437136</v>
+        <v>46032347</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>1397696</v>
+        <v>1521714</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturing</t>
+          <t>AI/Edge Computing</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>CIFR</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SEMTECH CORP</t>
+          <t>CIPHER DIGITAL INC</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>89213986</v>
+        <v>87867021</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>0.01377145298249926</v>
-      </c>
-      <c r="E31" s="7" t="n">
-        <v>46032347</v>
+        <v>0.01517341455320857</v>
+      </c>
+      <c r="E31" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>1521714</v>
+        <v>87867021</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>AI/Edge Computing</t>
+          <t>AI/Datacenter Power</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CIFR</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CIPHER DIGITAL INC</t>
+          <t>TESLA INC</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>87867021</v>
+        <v>85918065</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>0.0135635296960476</v>
-      </c>
-      <c r="E32" s="20" t="n">
-        <v>0</v>
+        <v>0.01483685691192967</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>9808836</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>87867021</v>
+        <v>1463688</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>AI/Datacenter Power</t>
+          <t>AI/EV</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>AMBQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TESLA INC</t>
+          <t>AMBIQ MICRO INC</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>85918065</v>
+        <v>77449961</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>0.01326268050050824</v>
+        <v>0.0133745329249621</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>9808836</v>
+        <v>54222186</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>1463688</v>
+        <v>1319908</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>AI/EV</t>
+          <t>AI/Edge Computing</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AMBQ</t>
+          <t>PDFS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AMBIQ MICRO INC</t>
+          <t>PDF SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>77449961</v>
+        <v>46617763</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>0.01195550769817527</v>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>54222186</v>
+        <v>0.00805024041434417</v>
+      </c>
+      <c r="E34" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>1319908</v>
+        <v>46617763</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>AI/Edge Computing</t>
+          <t>Semiconductor Supply Chain</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PDFS</t>
+          <t>ROG</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PDF SOLUTIONS INC</t>
+          <t>ROGERS CORP</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>46617763</v>
+        <v>30995890</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>0.007196117560578376</v>
-      </c>
-      <c r="E35" s="20" t="n">
-        <v>0</v>
+        <v>0.005352559846266461</v>
+      </c>
+      <c r="E35" s="7" t="n">
+        <v>10495194</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>46617763</v>
+        <v>528193</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -24824,25 +24794,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ROG</t>
+          <t>VECO</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ROGERS CORP</t>
+          <t>VEECO INSTRS INC DEL</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>30995890</v>
+        <v>18034260</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>0.004784658335809801</v>
+        <v>0.003114266308634125</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>10495194</v>
+        <v>9810730</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>528193</v>
+        <v>302897</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -24853,56 +24823,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>VECO</t>
+          <t>FRVO</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>VEECO INSTRS INC DEL</t>
+          <t>FERVO ENERGY CO</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>18034260</v>
+        <v>291102</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>0.002783845614343103</v>
-      </c>
-      <c r="E37" s="7" t="n">
-        <v>9810730</v>
+        <v>5.026927364782426e-05</v>
+      </c>
+      <c r="E37" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>302897</v>
+        <v>291102</v>
       </c>
       <c r="G37" t="inlineStr">
-        <is>
-          <t>Semiconductor Supply Chain</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>FRVO</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>FERVO ENERGY CO</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>291102</v>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>4.493575150998744e-05</v>
-      </c>
-      <c r="E38" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>291102</v>
-      </c>
-      <c r="G38" t="inlineStr">
         <is>
           <t>AI/Datacenter Power</t>
         </is>
@@ -24919,7 +24860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I199"/>
+  <dimension ref="A1:I195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -24979,13 +24920,13 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0.1555532496550355</v>
+        <v>0.1740162033782683</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0.1148261809171812</v>
       </c>
       <c r="D4" s="19" t="n">
-        <v>0.04072706873785423</v>
+        <v>0.05919002246108706</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -25001,13 +24942,13 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.1267516543935302</v>
+        <v>0.1417960840959038</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>0.06258771818496679</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>0.06416393620856338</v>
+        <v>0.07920836591093698</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -25019,671 +24960,662 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI/Datacenter Chips</t>
+          <t>Hyperscalers (quasi-index)</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.1060990491965794</v>
+        <v>0.1092205198010435</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0</v>
+        <v>0.08726640877550292</v>
       </c>
       <c r="D6" s="19" t="n">
-        <v>0.1060990491965794</v>
+        <v>0.02195411102554061</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>687329006</v>
+        <v>206859970</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Hyperscalers (quasi-index)</t>
+          <t>AI/Datacenter Optical</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0.09763232649739663</v>
+        <v>0.1020662051749379</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.08726640877550292</v>
-      </c>
-      <c r="D7" s="19" t="n">
-        <v>0.01036591772189372</v>
+        <v>0.1464221354555144</v>
+      </c>
+      <c r="D7" s="21" t="n">
+        <v>-0.04435593028057653</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>206859970</v>
+        <v>2</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-177847583</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI/Datacenter Optical</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>0.09123707785077395</v>
+        <v>0.05164331168546231</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.1464221354555144</v>
-      </c>
-      <c r="D8" s="21" t="n">
-        <v>-0.05518505760474044</v>
+        <v>0.02870056978847075</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>0.02294274189699156</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>-177847583</v>
+        <v>1</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>79735588</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>AI/World Models</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.04616400541827215</v>
+        <v>0.05056689937700833</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.02870056978847075</v>
-      </c>
-      <c r="D9" s="19" t="n">
-        <v>0.01746343562980141</v>
+        <v>0.06620107137492426</v>
+      </c>
+      <c r="D9" s="21" t="n">
+        <v>-0.01563417199791593</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="7" t="n">
-        <v>79735588</v>
+      <c r="F9" s="6" t="n">
+        <v>-61146996</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI/World Models</t>
+          <t>Enterprise SaaS</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>0.04520179943228864</v>
+        <v>0.05006887400086479</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.06620107137492426</v>
+        <v>0.07416474379556449</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>-0.02099927194263561</v>
+        <v>-0.0240958697946997</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>-61146996</v>
+        <v>-88678924</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Enterprise SaaS</t>
+          <t>AI/Edge Computing</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>0.0447566140750297</v>
+        <v>0.04736848588717928</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.07416474379556449</v>
-      </c>
-      <c r="D11" s="21" t="n">
-        <v>-0.02940812972053479</v>
+        <v>0.03459264813091067</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>0.01277583775626861</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="6" t="n">
-        <v>-88678924</v>
+      <c r="F11" s="7" t="n">
+        <v>29763477</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI/Edge Computing</t>
+          <t>Nvidia GPU moat / CUDA ecosystem</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>0.04234273457266797</v>
+        <v>0.0431664581658823</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.03459264813091067</v>
-      </c>
-      <c r="D12" s="19" t="n">
-        <v>0.007750086441757302</v>
+        <v>0.0530503338279851</v>
+      </c>
+      <c r="D12" s="21" t="n">
+        <v>-0.00988387566210279</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>29763477</v>
+        <v>139863</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nvidia GPU moat / CUDA ecosystem</t>
+          <t>Neoclouds as durable model</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>0.03858653799729827</v>
+        <v>0.03958250220045498</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.0530503338279851</v>
-      </c>
-      <c r="D13" s="21" t="n">
-        <v>-0.01446379583068682</v>
+        <v>0.01689197341723403</v>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>0.02269052878322096</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>139863</v>
+        <v>131118329</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Neoclouds as durable model</t>
+          <t>E-commerce</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>0.0353828363521652</v>
+        <v>0.02576370281402291</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.01689197341723403</v>
-      </c>
-      <c r="D14" s="19" t="n">
-        <v>0.01849086293493117</v>
+        <v>0.03627555869178559</v>
+      </c>
+      <c r="D14" s="21" t="n">
+        <v>-0.01051185587776267</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="7" t="n">
-        <v>131118329</v>
+      <c r="F14" s="6" t="n">
+        <v>-53049731</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E-commerce</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>0.02303019844167185</v>
+        <v>0.01835398369595954</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.03627555869178559</v>
+        <v>0.04638973738265921</v>
       </c>
       <c r="D15" s="21" t="n">
-        <v>-0.01324536025011374</v>
+        <v>-0.02803575368669967</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-53049731</v>
+        <v>-103404250</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>0.01640664347684871</v>
+        <v>0.01792779384439325</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.04638973738265921</v>
+        <v>0.04197004849086948</v>
       </c>
       <c r="D16" s="21" t="n">
-        <v>-0.0299830939058105</v>
+        <v>-0.02404225464647623</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>-103404250</v>
+        <v>-111143258</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>AI/Datacenter Power</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>0.01602567196331084</v>
+        <v>0.01760518544216707</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.04197004849086948</v>
+        <v>0.01918325473661888</v>
       </c>
       <c r="D17" s="21" t="n">
-        <v>-0.02594437652755864</v>
+        <v>-0.001578069294451812</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>-111143258</v>
+        <v>3</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>23208000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI/Datacenter Power</t>
+          <t>Semiconductor Supply Chain</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>0.01573729200582368</v>
+        <v>0.01651706656924476</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.01918325473661888</v>
+        <v>0.02002135006874856</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>-0.003445962730795202</v>
+        <v>-0.003504283499503804</v>
       </c>
       <c r="E18" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="7" t="n">
-        <v>23208000</v>
+      <c r="F18" s="6" t="n">
+        <v>-6839171</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Semiconductor Supply Chain</t>
+          <t>Semiconductor Manufacturing</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>0.01476462151073128</v>
+        <v>0.01600570153603687</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>0.02002135006874856</v>
-      </c>
-      <c r="D19" s="21" t="n">
-        <v>-0.00525672855801728</v>
+        <v>0.01217190712008808</v>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>0.003833794415948788</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-6839171</v>
+        <v>-19712201</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturing</t>
+          <t>Humanoid robotics / Tesla Optimus</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>0.01430751182133913</v>
+        <v>0.01483685691192967</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>0.01217190712008808</v>
-      </c>
-      <c r="D20" s="19" t="n">
-        <v>0.002135604701251044</v>
+        <v>0.01818548810253011</v>
+      </c>
+      <c r="D20" s="21" t="n">
+        <v>-0.003348631190600439</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="6" t="n">
-        <v>-19712201</v>
+      <c r="F20" s="7" t="n">
+        <v>1463688</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Humanoid robotics / Tesla Optimus</t>
+          <t>Industrial IoT</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>0.01326268050050824</v>
+        <v>0.01292892089327872</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.01818548810253011</v>
-      </c>
-      <c r="D21" s="21" t="n">
-        <v>-0.004922807602021877</v>
+        <v>0</v>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>0.01292892089327872</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>1463688</v>
+        <v>74869487</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Industrial IoT</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>0.01155717467936405</v>
+        <v>0.01204802207814093</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0</v>
+        <v>0.009905337859333493</v>
       </c>
       <c r="D22" s="19" t="n">
-        <v>0.01155717467936405</v>
+        <v>0.002142684218807435</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>74869487</v>
+        <v>1188896</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Web / SMB SaaS</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>0.01076973839095078</v>
+        <v>0.01142668154678749</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0.009905337859333493</v>
-      </c>
-      <c r="D23" s="19" t="n">
-        <v>0.0008644005316172853</v>
+        <v>0.01427220699455487</v>
+      </c>
+      <c r="D23" s="21" t="n">
+        <v>-0.002845525447767374</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>1188896</v>
+        <v>36660956</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Web / SMB SaaS</t>
+          <t>Payments</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>0.01021432149920124</v>
+        <v>0.008304104718836079</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0.01427220699455487</v>
+        <v>0.01131341626952442</v>
       </c>
       <c r="D24" s="21" t="n">
-        <v>-0.004057885495353626</v>
+        <v>-0.003009311550688344</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>36660956</v>
+        <v>958464</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Payments</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>0.007423047103738744</v>
+        <v>0.006792856683061859</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>0.01131341626952442</v>
+        <v>0.009376222072631753</v>
       </c>
       <c r="D25" s="21" t="n">
-        <v>-0.00389036916578568</v>
+        <v>-0.002583365389569895</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>958464</v>
+        <v>405953</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>0.006072141047660364</v>
+        <v>0.00579045125440373</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>0.009376222072631753</v>
+        <v>0.03339248989499596</v>
       </c>
       <c r="D26" s="21" t="n">
-        <v>-0.003304081024971389</v>
+        <v>-0.02760203864059223</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
-      </c>
-      <c r="F26" s="7" t="n">
-        <v>405953</v>
+        <v>1</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-116539107</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Healthcare/Diagnostics</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>0.005176089881892354</v>
+        <v>0.004893114275227872</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>0.03339248989499596</v>
-      </c>
-      <c r="D27" s="21" t="n">
-        <v>-0.02821640001310361</v>
+        <v>0</v>
+      </c>
+      <c r="D27" s="19" t="n">
+        <v>0.004893114275227872</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="6" t="n">
-        <v>-116539107</v>
+      <c r="F27" s="7" t="n">
+        <v>28335308</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Healthcare/Diagnostics</t>
+          <t>AdTech / digital advertising</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>0.004373959503015985</v>
+        <v>0.0007209869821754592</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="19" t="n">
-        <v>0.004373959503015985</v>
+        <v>0.0006198956625919947</v>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>0.0001010913195834644</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>28335308</v>
+        <v>71145</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AdTech / digital advertising</t>
+          <t>Quantum Computing</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>0.0006444909488835318</v>
+        <v>0.0005625395274741292</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>0.0006198956625919947</v>
-      </c>
-      <c r="D29" s="18" t="n">
-        <v>2.459528629153711e-05</v>
+        <v>0</v>
+      </c>
+      <c r="D29" s="19" t="n">
+        <v>0.0005625395274741292</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>71145</v>
+        <v>3257584</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Quantum Computing</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>0.000502854618473631</v>
+        <v>2.648745985418006e-05</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="19" t="n">
-        <v>0.000502854618473631</v>
+        <v>5.835831762618304e-05</v>
+      </c>
+      <c r="D30" s="18" t="n">
+        <v>-3.187085777200297e-05</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>3257584</v>
+        <v>2616</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>2.367716554801899e-05</v>
+        <v>0</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>5.835831762618304e-05</v>
-      </c>
-      <c r="D31" s="18" t="n">
-        <v>-3.468115207816405e-05</v>
+        <v>0.007209974000570652</v>
+      </c>
+      <c r="D31" s="21" t="n">
+        <v>-0.007209974000570652</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="7" t="n">
-        <v>2616</v>
+        <v>0</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-29594609</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Defense/Security</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>0.007209974000570652</v>
+        <v>0.01056325113664677</v>
       </c>
       <c r="D32" s="21" t="n">
-        <v>-0.007209974000570652</v>
+        <v>-0.01056325113664677</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>-29594609</v>
+        <v>-43358726</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Defense/Security</t>
+          <t>Gaming/Metaverse</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>0.01056325113664677</v>
+        <v>0.01906660534174885</v>
       </c>
       <c r="D33" s="21" t="n">
-        <v>-0.01056325113664677</v>
+        <v>-0.01906660534174885</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>-43358726</v>
+        <v>-78262242</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gaming/Metaverse</t>
+          <t>AI/Data Infrastructure</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
         <v>0</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>0.01906660534174885</v>
+        <v>0.005321114188220493</v>
       </c>
       <c r="D34" s="21" t="n">
-        <v>-0.01906660534174885</v>
+        <v>-0.005321114188220493</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>-78262242</v>
+        <v>-21841451</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>AI/Data Infrastructure</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>0.005321114188220493</v>
-      </c>
-      <c r="D35" s="21" t="n">
-        <v>-0.005321114188220493</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="6" t="n">
-        <v>-21841451</v>
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>[memo] Orbital / space-based compute — SPCX (IPO reclass)</t>
+        </is>
+      </c>
+      <c r="B35" s="25" t="n">
+        <v>0.4189079214879446</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>[memo] Orbital / space-based compute — SPCX (IPO reclass)</t>
+          <t>[memo] AI/Datacenter Chips — CBRS (IPO reclass)</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
-        <v>0.4189079214879446</v>
+        <v>0.06165331702579317</v>
       </c>
       <c r="E36" s="9" t="n">
         <v>1</v>
@@ -25714,7 +25646,7 @@
     <row r="42">
       <c r="A42" s="23" t="inlineStr">
         <is>
-          <t>AI/Datacenter Networking   —   wt 15.6% (Q1 11.5%, Δ +4.1pp) · 3 held</t>
+          <t>AI/Datacenter Networking   —   wt 17.4% (Q1 11.5%, Δ +5.9pp) · 3 held</t>
         </is>
       </c>
       <c r="B42" s="24" t="n"/>
@@ -25788,10 +25720,10 @@
         <v>587736321</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>0.09072549578446804</v>
+        <v>0.1014939023198552</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>0.0008547646788846385</v>
+        <v>0.01162317121427178</v>
       </c>
       <c r="F44" s="7" t="n">
         <v>218846066</v>
@@ -25825,10 +25757,10 @@
         <v>307109056</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>0.04740666923237497</v>
+        <v>0.05303346997199945</v>
       </c>
       <c r="E45" s="18" t="n">
-        <v>0.02245121942077712</v>
+        <v>0.0280780201604016</v>
       </c>
       <c r="F45" s="7" t="n">
         <v>204675014</v>
@@ -25858,10 +25790,10 @@
         <v>112856966</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>0.01742108463819246</v>
+        <v>0.01948883108641369</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>0.01742108463819246</v>
+        <v>0.01948883108641369</v>
       </c>
       <c r="F46" s="7" t="n">
         <v>112856966</v>
@@ -25879,7 +25811,7 @@
     <row r="48">
       <c r="A48" s="23" t="inlineStr">
         <is>
-          <t>DRAM / HBM memory bottleneck   —   wt 12.7% (Q1 6.3%, Δ +6.4pp) · 1 held</t>
+          <t>DRAM / HBM memory bottleneck   —   wt 14.2% (Q1 6.3%, Δ +7.9pp) · 1 held</t>
         </is>
       </c>
       <c r="B48" s="24" t="n"/>
@@ -25953,10 +25885,10 @@
         <v>821120352</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>0.1267516543935302</v>
+        <v>0.1417960840959038</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>0.06416393620856338</v>
+        <v>0.07920836591093698</v>
       </c>
       <c r="F50" s="7" t="n">
         <v>564218032</v>
@@ -25978,7 +25910,7 @@
     <row r="52">
       <c r="A52" s="23" t="inlineStr">
         <is>
-          <t>AI/Datacenter Chips   —   wt 10.6% (Q1 0.0%, Δ +10.6pp) · 1 held</t>
+          <t>Hyperscalers (quasi-index)   —   wt 10.9% (Q1 8.7%, Δ +2.2pp) · 3 held</t>
         </is>
       </c>
       <c r="B52" s="24" t="n"/>
@@ -26040,500 +25972,504 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CBRS</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CEREBRAS SYSTEMS INC</t>
+          <t>AMAZON COM INC</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>687329006</v>
+        <v>231101376</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>0.1060990491965794</v>
+        <v>0.03990799895065209</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>0.1060990491965794</v>
+        <v>-0.008475339757315438</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>687329006</v>
+        <v>32503435</v>
       </c>
       <c r="G54" s="7" t="n">
-        <v>687329006</v>
+        <v>3829885</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
+          <t>DRIFT_DOWN</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Custom ASIC failure thesis, Trainium / Amazon custom silicon, Switched scaleup networks, AI capex ROI positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>META PLATFORMS INC</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>226876313</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>0.03917838923266219</v>
+      </c>
+      <c r="E55" s="18" t="n">
+        <v>0.03917838923266219</v>
+      </c>
+      <c r="F55" s="7" t="n">
+        <v>226876313</v>
+      </c>
+      <c r="G55" s="7" t="n">
+        <v>226876313</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>AI capex ROI positive, Meta AI transformation</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="23" t="inlineStr">
-        <is>
-          <t>Hyperscalers (quasi-index)   —   wt 9.8% (Q1 8.7%, Δ +1.0pp) · 3 held</t>
-        </is>
-      </c>
-      <c r="B56" s="24" t="n"/>
-      <c r="C56" s="24" t="n"/>
-      <c r="D56" s="24" t="n"/>
-      <c r="E56" s="24" t="n"/>
-      <c r="F56" s="24" t="n"/>
-      <c r="G56" s="24" t="n"/>
-      <c r="H56" s="24" t="n"/>
-      <c r="I56" s="24" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ALPHABET INC</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>174502342</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>0.03013413161772924</v>
+      </c>
+      <c r="E56" s="18" t="n">
+        <v>-0.008748938449806154</v>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>14899928</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>-23846228</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>ACTIVE_TRIM</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Custom ASIC failure thesis, AI capex ROI positive, Google TPU competitive position, Google AI distribution moat</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="23" t="inlineStr">
+        <is>
+          <t>AI/Datacenter Optical   —   wt 10.2% (Q1 14.6%, Δ -4.4pp) · 2 held · 1 exited</t>
+        </is>
+      </c>
+      <c r="B58" s="24" t="n"/>
+      <c r="C58" s="24" t="n"/>
+      <c r="D58" s="24" t="n"/>
+      <c r="E58" s="24" t="n"/>
+      <c r="F58" s="24" t="n"/>
+      <c r="G58" s="24" t="n"/>
+      <c r="H58" s="24" t="n"/>
+      <c r="I58" s="24" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>company</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>market_value</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>wt_eq%</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>Δwt_pp</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>value_Δ$</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>Trading_$</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
+      <c r="H59" s="3" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="I57" s="3" t="inlineStr">
+      <c r="I59" s="3" t="inlineStr">
         <is>
           <t>also_in (other theses)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>AMAZON COM INC</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="n">
-        <v>231101376</v>
-      </c>
-      <c r="D58" s="5" t="n">
-        <v>0.03567379820664982</v>
-      </c>
-      <c r="E58" s="18" t="n">
-        <v>-0.01270954050131771</v>
-      </c>
-      <c r="F58" s="7" t="n">
-        <v>32503435</v>
-      </c>
-      <c r="G58" s="7" t="n">
-        <v>3829885</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>DRIFT_DOWN</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Custom ASIC failure thesis, Trainium / Amazon custom silicon, Switched scaleup networks, AI capex ROI positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>META PLATFORMS INC</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="n">
-        <v>226876313</v>
-      </c>
-      <c r="D59" s="5" t="n">
-        <v>0.03502159938602323</v>
-      </c>
-      <c r="E59" s="18" t="n">
-        <v>0.03502159938602323</v>
-      </c>
-      <c r="F59" s="7" t="n">
-        <v>226876313</v>
-      </c>
-      <c r="G59" s="7" t="n">
-        <v>226876313</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>AI capex ROI positive, Meta AI transformation</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>CIEN</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ALPHABET INC</t>
+          <t>CIENA CORP</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>174502342</v>
+        <v>337760862</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>0.02693692890472359</v>
+        <v>0.05832661128883693</v>
       </c>
       <c r="E60" s="18" t="n">
-        <v>-0.01194614116281181</v>
+        <v>-0.005687397704950108</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>14899928</v>
-      </c>
-      <c r="G60" s="6" t="n">
-        <v>-23846228</v>
+        <v>75004080</v>
+      </c>
+      <c r="G60" s="7" t="n">
+        <v>5746420</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>ACTIVE_TRIM</t>
+          <t>DRIFT_DOWN</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Custom ASIC failure thesis, AI capex ROI positive, Google TPU competitive position, Google AI distribution moat</t>
+          <t>Optical networking / interconnect</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>COHR</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>COHERENT CORP</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>253289581</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>0.04373959388610092</v>
+      </c>
+      <c r="E61" s="18" t="n">
+        <v>0.007111032688425127</v>
+      </c>
+      <c r="F61" s="7" t="n">
+        <v>102941196</v>
+      </c>
+      <c r="G61" s="7" t="n">
+        <v>4316291</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>DRIFT_DOWN</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Optical networking / interconnect</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="23" t="inlineStr">
-        <is>
-          <t>AI/Datacenter Optical   —   wt 9.1% (Q1 14.6%, Δ -5.5pp) · 2 held · 1 exited</t>
-        </is>
-      </c>
-      <c r="B62" s="24" t="n"/>
-      <c r="C62" s="24" t="n"/>
-      <c r="D62" s="24" t="n"/>
-      <c r="E62" s="24" t="n"/>
-      <c r="F62" s="24" t="n"/>
-      <c r="G62" s="24" t="n"/>
-      <c r="H62" s="24" t="n"/>
-      <c r="I62" s="24" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>LITE</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="18" t="n">
+        <v>-0.04577956526405155</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>-187910294</v>
+      </c>
+      <c r="G62" s="6" t="n">
+        <v>-187910294</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="23" t="inlineStr">
+        <is>
+          <t>Cybersecurity   —   wt 5.2% (Q1 2.9%, Δ +2.3pp) · 1 held · 1 exited</t>
+        </is>
+      </c>
+      <c r="B64" s="24" t="n"/>
+      <c r="C64" s="24" t="n"/>
+      <c r="D64" s="24" t="n"/>
+      <c r="E64" s="24" t="n"/>
+      <c r="F64" s="24" t="n"/>
+      <c r="G64" s="24" t="n"/>
+      <c r="H64" s="24" t="n"/>
+      <c r="I64" s="24" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>company</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>market_value</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>wt_eq%</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>Δwt_pp</t>
         </is>
       </c>
-      <c r="F63" s="3" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>value_Δ$</t>
         </is>
       </c>
-      <c r="G63" s="3" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>Trading_$</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
+      <c r="H65" s="3" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="I63" s="3" t="inlineStr">
+      <c r="I65" s="3" t="inlineStr">
         <is>
           <t>also_in (other theses)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>CIEN</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>CIENA CORP</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="n">
-        <v>337760862</v>
-      </c>
-      <c r="D64" s="5" t="n">
-        <v>0.05213821328823285</v>
-      </c>
-      <c r="E64" s="18" t="n">
-        <v>-0.01187579570555418</v>
-      </c>
-      <c r="F64" s="7" t="n">
-        <v>75004080</v>
-      </c>
-      <c r="G64" s="7" t="n">
-        <v>5746420</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>DRIFT_DOWN</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Optical networking / interconnect</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>COHR</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>COHERENT CORP</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="n">
-        <v>253289581</v>
-      </c>
-      <c r="D65" s="5" t="n">
-        <v>0.03909886456254109</v>
-      </c>
-      <c r="E65" s="18" t="n">
-        <v>0.002470303364865298</v>
-      </c>
-      <c r="F65" s="7" t="n">
-        <v>102941196</v>
-      </c>
-      <c r="G65" s="7" t="n">
-        <v>4316291</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>DRIFT_DOWN</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Optical networking / interconnect</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>LITE</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
+          <t>PANW</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>PALO ALTO NETWORKS INC</t>
+        </is>
+      </c>
       <c r="C66" s="4" t="n">
+        <v>299058853</v>
+      </c>
+      <c r="D66" s="5" t="n">
+        <v>0.05164331168546231</v>
+      </c>
+      <c r="E66" s="18" t="n">
+        <v>0.0297007053394306</v>
+      </c>
+      <c r="F66" s="7" t="n">
+        <v>208991558</v>
+      </c>
+      <c r="G66" s="7" t="n">
+        <v>107474840</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>RBRK</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D66" s="5" t="n">
+      <c r="D67" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E66" s="18" t="n">
-        <v>-0.04577956526405155</v>
-      </c>
-      <c r="F66" s="6" t="n">
-        <v>-187910294</v>
-      </c>
-      <c r="G66" s="6" t="n">
-        <v>-187910294</v>
-      </c>
-      <c r="H66" t="inlineStr">
+      <c r="E67" s="18" t="n">
+        <v>-0.006757963442439043</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>-27739252</v>
+      </c>
+      <c r="G67" s="6" t="n">
+        <v>-27739252</v>
+      </c>
+      <c r="H67" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="23" t="inlineStr">
-        <is>
-          <t>Cybersecurity   —   wt 4.6% (Q1 2.9%, Δ +1.7pp) · 1 held · 1 exited</t>
-        </is>
-      </c>
-      <c r="B68" s="24" t="n"/>
-      <c r="C68" s="24" t="n"/>
-      <c r="D68" s="24" t="n"/>
-      <c r="E68" s="24" t="n"/>
-      <c r="F68" s="24" t="n"/>
-      <c r="G68" s="24" t="n"/>
-      <c r="H68" s="24" t="n"/>
-      <c r="I68" s="24" t="n"/>
-    </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="A69" s="23" t="inlineStr">
+        <is>
+          <t>AI/World Models   —   wt 5.1% (Q1 6.6%, Δ -1.6pp) · 1 held</t>
+        </is>
+      </c>
+      <c r="B69" s="24" t="n"/>
+      <c r="C69" s="24" t="n"/>
+      <c r="D69" s="24" t="n"/>
+      <c r="E69" s="24" t="n"/>
+      <c r="F69" s="24" t="n"/>
+      <c r="G69" s="24" t="n"/>
+      <c r="H69" s="24" t="n"/>
+      <c r="I69" s="24" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>company</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>market_value</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>wt_eq%</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>Δwt_pp</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr">
         <is>
           <t>value_Δ$</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="G70" s="3" t="inlineStr">
         <is>
           <t>Trading_$</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
+      <c r="H70" s="3" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="I69" s="3" t="inlineStr">
+      <c r="I70" s="3" t="inlineStr">
         <is>
           <t>also_in (other theses)</t>
         </is>
       </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>PANW</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>PALO ALTO NETWORKS INC</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="n">
-        <v>299058853</v>
-      </c>
-      <c r="D70" s="5" t="n">
-        <v>0.04616400541827215</v>
-      </c>
-      <c r="E70" s="18" t="n">
-        <v>0.02422139907224045</v>
-      </c>
-      <c r="F70" s="7" t="n">
-        <v>208991558</v>
-      </c>
-      <c r="G70" s="7" t="n">
-        <v>107474840</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>RBRK</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>UNITY SOFTWARE INC</t>
+        </is>
+      </c>
       <c r="C71" s="4" t="n">
-        <v>0</v>
+        <v>292825507</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>0</v>
+        <v>0.05056689937700833</v>
       </c>
       <c r="E71" s="18" t="n">
-        <v>-0.006757963442439043</v>
-      </c>
-      <c r="F71" s="6" t="n">
-        <v>-27739252</v>
+        <v>-0.01563417199791593</v>
+      </c>
+      <c r="F71" s="7" t="n">
+        <v>21091542</v>
       </c>
       <c r="G71" s="6" t="n">
-        <v>-27739252</v>
+        <v>-61146996</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>EXIT</t>
+          <t>ACTIVE_TRIM</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Unity / world models</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="23" t="inlineStr">
         <is>
-          <t>AI/World Models   —   wt 4.5% (Q1 6.6%, Δ -2.1pp) · 1 held</t>
+          <t>Enterprise SaaS   —   wt 5.0% (Q1 7.4%, Δ -2.4pp) · 3 held · 3 exited</t>
         </is>
       </c>
       <c r="B73" s="24" t="n"/>
@@ -26595,454 +26531,454 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>UNITY SOFTWARE INC</t>
+          <t>TWILIO INC</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>292825507</v>
+        <v>148627340</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>0.04520179943228864</v>
+        <v>0.02566587802903524</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>-0.02099927194263561</v>
+        <v>-0.0025838442650186</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>21091542</v>
+        <v>32671376</v>
       </c>
       <c r="G75" s="6" t="n">
-        <v>-61146996</v>
+        <v>-41526801</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>ACTIVE_TRIM</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Unity / world models</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>GTLB</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>GITLAB INC</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>102982850</v>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>0.01778370834856112</v>
+      </c>
+      <c r="E76" s="18" t="n">
+        <v>0.01778370834856112</v>
+      </c>
+      <c r="F76" s="7" t="n">
+        <v>102982850</v>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>102982850</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="23" t="inlineStr">
-        <is>
-          <t>Enterprise SaaS   —   wt 4.5% (Q1 7.4%, Δ -2.9pp) · 3 held · 3 exited</t>
-        </is>
-      </c>
-      <c r="B77" s="24" t="n"/>
-      <c r="C77" s="24" t="n"/>
-      <c r="D77" s="24" t="n"/>
-      <c r="E77" s="24" t="n"/>
-      <c r="F77" s="24" t="n"/>
-      <c r="G77" s="24" t="n"/>
-      <c r="H77" s="24" t="n"/>
-      <c r="I77" s="24" t="n"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>TTAN</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SERVICETITAN INC</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="n">
+        <v>38331325</v>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>0.006619287623268433</v>
+      </c>
+      <c r="E77" s="18" t="n">
+        <v>0.006619287623268433</v>
+      </c>
+      <c r="F77" s="7" t="n">
+        <v>38331325</v>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>38331325</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="inlineStr">
-        <is>
-          <t>market_value</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>wt_eq%</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="inlineStr">
-        <is>
-          <t>Δwt_pp</t>
-        </is>
-      </c>
-      <c r="F78" s="3" t="inlineStr">
-        <is>
-          <t>value_Δ$</t>
-        </is>
-      </c>
-      <c r="G78" s="3" t="inlineStr">
-        <is>
-          <t>Trading_$</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>change</t>
-        </is>
-      </c>
-      <c r="I78" s="3" t="inlineStr">
-        <is>
-          <t>also_in (other theses)</t>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ZM</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="18" t="n">
+        <v>-0.02576609693751038</v>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>-105761486</v>
+      </c>
+      <c r="G78" s="6" t="n">
+        <v>-105761486</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>EXIT</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TWLO</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>TWILIO INC</t>
-        </is>
-      </c>
+          <t>HUBS</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
       <c r="C79" s="4" t="n">
-        <v>148627340</v>
+        <v>0</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>0.02294275277335922</v>
+        <v>0</v>
       </c>
       <c r="E79" s="18" t="n">
-        <v>-0.005306969520694618</v>
-      </c>
-      <c r="F79" s="7" t="n">
-        <v>32671376</v>
+        <v>-0.01380359098548187</v>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>-56659272</v>
       </c>
       <c r="G79" s="6" t="n">
-        <v>-41526801</v>
+        <v>-56659272</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>ACTIVE_TRIM</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GTLB</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>GITLAB INC</t>
-        </is>
-      </c>
+          <t>M6191J100</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
       <c r="C80" s="4" t="n">
-        <v>102982850</v>
+        <v>0</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>0.01589687380158951</v>
+        <v>0</v>
       </c>
       <c r="E80" s="18" t="n">
-        <v>0.01589687380158951</v>
-      </c>
-      <c r="F80" s="7" t="n">
-        <v>102982850</v>
-      </c>
-      <c r="G80" s="7" t="n">
-        <v>102982850</v>
+        <v>-0.006345333578518404</v>
+      </c>
+      <c r="F80" s="6" t="n">
+        <v>-26045540</v>
+      </c>
+      <c r="G80" s="6" t="n">
+        <v>-26045540</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>TTAN</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>SERVICETITAN INC</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v>38331325</v>
-      </c>
-      <c r="D81" s="5" t="n">
-        <v>0.005916987500080966</v>
-      </c>
-      <c r="E81" s="18" t="n">
-        <v>0.005916987500080966</v>
-      </c>
-      <c r="F81" s="7" t="n">
-        <v>38331325</v>
-      </c>
-      <c r="G81" s="7" t="n">
-        <v>38331325</v>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>ZM</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" s="18" t="n">
-        <v>-0.02576609693751038</v>
-      </c>
-      <c r="F82" s="6" t="n">
-        <v>-105761486</v>
-      </c>
-      <c r="G82" s="6" t="n">
-        <v>-105761486</v>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
+      <c r="A82" s="23" t="inlineStr">
+        <is>
+          <t>AI/Edge Computing   —   wt 4.7% (Q1 3.5%, Δ +1.3pp) · 3 held</t>
+        </is>
+      </c>
+      <c r="B82" s="24" t="n"/>
+      <c r="C82" s="24" t="n"/>
+      <c r="D82" s="24" t="n"/>
+      <c r="E82" s="24" t="n"/>
+      <c r="F82" s="24" t="n"/>
+      <c r="G82" s="24" t="n"/>
+      <c r="H82" s="24" t="n"/>
+      <c r="I82" s="24" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>HUBS</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="18" t="n">
-        <v>-0.01380359098548187</v>
-      </c>
-      <c r="F83" s="6" t="n">
-        <v>-56659272</v>
-      </c>
-      <c r="G83" s="6" t="n">
-        <v>-56659272</v>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>EXIT</t>
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>market_value</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>wt_eq%</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>Δwt_pp</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>value_Δ$</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>Trading_$</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>change</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>also_in (other theses)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>M6191J100</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
+          <t>AKAM</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>AKAMAI TECHNOLOGIES INC</t>
+        </is>
+      </c>
       <c r="C84" s="4" t="n">
-        <v>0</v>
+        <v>107640016</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>0</v>
+        <v>0.0185879362551964</v>
       </c>
       <c r="E84" s="18" t="n">
-        <v>-0.006345333578518404</v>
-      </c>
-      <c r="F84" s="6" t="n">
-        <v>-26045540</v>
-      </c>
-      <c r="G84" s="6" t="n">
-        <v>-26045540</v>
+        <v>-0.000518035650538149</v>
+      </c>
+      <c r="F84" s="7" t="n">
+        <v>29216187</v>
+      </c>
+      <c r="G84" s="7" t="n">
+        <v>26921855</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>CDN / token delivery path</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>SMTC</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SEMTECH CORP</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="n">
+        <v>89213986</v>
+      </c>
+      <c r="D85" s="5" t="n">
+        <v>0.01540601670702078</v>
+      </c>
+      <c r="E85" s="18" t="n">
+        <v>0.005256635239750054</v>
+      </c>
+      <c r="F85" s="7" t="n">
+        <v>47554061</v>
+      </c>
+      <c r="G85" s="7" t="n">
+        <v>1521714</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="23" t="inlineStr">
-        <is>
-          <t>AI/Edge Computing   —   wt 4.2% (Q1 3.5%, Δ +0.8pp) · 3 held</t>
-        </is>
-      </c>
-      <c r="B86" s="24" t="n"/>
-      <c r="C86" s="24" t="n"/>
-      <c r="D86" s="24" t="n"/>
-      <c r="E86" s="24" t="n"/>
-      <c r="F86" s="24" t="n"/>
-      <c r="G86" s="24" t="n"/>
-      <c r="H86" s="24" t="n"/>
-      <c r="I86" s="24" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="inlineStr">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>AMBQ</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>AMBIQ MICRO INC</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="n">
+        <v>77449961</v>
+      </c>
+      <c r="D86" s="5" t="n">
+        <v>0.0133745329249621</v>
+      </c>
+      <c r="E86" s="18" t="n">
+        <v>0.008037238167056706</v>
+      </c>
+      <c r="F86" s="7" t="n">
+        <v>55542094</v>
+      </c>
+      <c r="G86" s="7" t="n">
+        <v>1319908</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="23" t="inlineStr">
+        <is>
+          <t>Nvidia GPU moat / CUDA ecosystem   —   wt 4.3% (Q1 5.3%, Δ -1.0pp) · 1 held</t>
+        </is>
+      </c>
+      <c r="B88" s="24" t="n"/>
+      <c r="C88" s="24" t="n"/>
+      <c r="D88" s="24" t="n"/>
+      <c r="E88" s="24" t="n"/>
+      <c r="F88" s="24" t="n"/>
+      <c r="G88" s="24" t="n"/>
+      <c r="H88" s="24" t="n"/>
+      <c r="I88" s="24" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="B87" s="3" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>company</t>
         </is>
       </c>
-      <c r="C87" s="3" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>market_value</t>
         </is>
       </c>
-      <c r="D87" s="3" t="inlineStr">
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>wt_eq%</t>
         </is>
       </c>
-      <c r="E87" s="3" t="inlineStr">
+      <c r="E89" s="3" t="inlineStr">
         <is>
           <t>Δwt_pp</t>
         </is>
       </c>
-      <c r="F87" s="3" t="inlineStr">
+      <c r="F89" s="3" t="inlineStr">
         <is>
           <t>value_Δ$</t>
         </is>
       </c>
-      <c r="G87" s="3" t="inlineStr">
+      <c r="G89" s="3" t="inlineStr">
         <is>
           <t>Trading_$</t>
         </is>
       </c>
-      <c r="H87" s="3" t="inlineStr">
+      <c r="H89" s="3" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="I87" s="3" t="inlineStr">
+      <c r="I89" s="3" t="inlineStr">
         <is>
           <t>also_in (other theses)</t>
         </is>
       </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>AKAM</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>AKAMAI TECHNOLOGIES INC</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="n">
-        <v>107640016</v>
-      </c>
-      <c r="D88" s="5" t="n">
-        <v>0.01661577389199343</v>
-      </c>
-      <c r="E88" s="18" t="n">
-        <v>-0.002490198013741114</v>
-      </c>
-      <c r="F88" s="7" t="n">
-        <v>29216187</v>
-      </c>
-      <c r="G88" s="7" t="n">
-        <v>26921855</v>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>CDN / token delivery path</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>SMTC</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>SEMTECH CORP</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="n">
-        <v>89213986</v>
-      </c>
-      <c r="D89" s="5" t="n">
-        <v>0.01377145298249926</v>
-      </c>
-      <c r="E89" s="18" t="n">
-        <v>0.003622071515228533</v>
-      </c>
-      <c r="F89" s="7" t="n">
-        <v>47554061</v>
-      </c>
-      <c r="G89" s="7" t="n">
-        <v>1521714</v>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AMBQ</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>AMBIQ MICRO INC</t>
+          <t>NVIDIA CORPORATION</t>
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>77449961</v>
+        <v>249970636</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>0.01195550769817527</v>
+        <v>0.0431664581658823</v>
       </c>
       <c r="E90" s="18" t="n">
-        <v>0.006618212940269881</v>
+        <v>-0.00988387566210279</v>
       </c>
       <c r="F90" s="7" t="n">
-        <v>55542094</v>
+        <v>32216191</v>
       </c>
       <c r="G90" s="7" t="n">
-        <v>1319908</v>
+        <v>139863</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>DRIFT_DOWN</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Switched scaleup networks, TSMC capacity discipline, Reasoning / inference-time compute, China AI distillation / export controls, Disaggregation prefill/decode, Open source AI bullish for hardware</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="23" t="inlineStr">
         <is>
-          <t>Nvidia GPU moat / CUDA ecosystem   —   wt 3.9% (Q1 5.3%, Δ -1.4pp) · 1 held</t>
+          <t>Neoclouds as durable model   —   wt 4.0% (Q1 1.7%, Δ +2.3pp) · 2 held</t>
         </is>
       </c>
       <c r="B92" s="24" t="n"/>
@@ -27104,1144 +27040,1144 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>NVIDIA CORPORATION</t>
+          <t>COREWEAVE INC</t>
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>249970636</v>
+        <v>211507071</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0.03858653799729827</v>
+        <v>0.03652433453067583</v>
       </c>
       <c r="E94" s="18" t="n">
-        <v>-0.01446379583068682</v>
+        <v>0.02122662473156895</v>
       </c>
       <c r="F94" s="7" t="n">
-        <v>32216191</v>
+        <v>148714925</v>
       </c>
       <c r="G94" s="7" t="n">
-        <v>139863</v>
+        <v>130826417</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>DRIFT_DOWN</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Switched scaleup networks, TSMC capacity discipline, Reasoning / inference-time compute, China AI distillation / export controls, Disaggregation prefill/decode, Open source AI bullish for hardware</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="23" t="inlineStr">
-        <is>
-          <t>Neoclouds as durable model   —   wt 3.5% (Q1 1.7%, Δ +1.8pp) · 2 held</t>
-        </is>
-      </c>
-      <c r="B96" s="24" t="n"/>
-      <c r="C96" s="24" t="n"/>
-      <c r="D96" s="24" t="n"/>
-      <c r="E96" s="24" t="n"/>
-      <c r="F96" s="24" t="n"/>
-      <c r="G96" s="24" t="n"/>
-      <c r="H96" s="24" t="n"/>
-      <c r="I96" s="24" t="n"/>
+          <t>Inference economics / token factories</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>NEBIUS GROUP N.V.</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>NEBIUS GROUP N.V.</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="n">
+        <v>17709401</v>
+      </c>
+      <c r="D95" s="5" t="n">
+        <v>0.003058167669779159</v>
+      </c>
+      <c r="E95" s="18" t="n">
+        <v>0.001463904051652009</v>
+      </c>
+      <c r="F95" s="7" t="n">
+        <v>11165465</v>
+      </c>
+      <c r="G95" s="7" t="n">
+        <v>291912</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="inlineStr">
+      <c r="A97" s="23" t="inlineStr">
+        <is>
+          <t>E-commerce   —   wt 2.6% (Q1 3.6%, Δ -1.1pp) · 2 held</t>
+        </is>
+      </c>
+      <c r="B97" s="24" t="n"/>
+      <c r="C97" s="24" t="n"/>
+      <c r="D97" s="24" t="n"/>
+      <c r="E97" s="24" t="n"/>
+      <c r="F97" s="24" t="n"/>
+      <c r="G97" s="24" t="n"/>
+      <c r="H97" s="24" t="n"/>
+      <c r="I97" s="24" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="B97" s="3" t="inlineStr">
+      <c r="B98" s="3" t="inlineStr">
         <is>
           <t>company</t>
         </is>
       </c>
-      <c r="C97" s="3" t="inlineStr">
+      <c r="C98" s="3" t="inlineStr">
         <is>
           <t>market_value</t>
         </is>
       </c>
-      <c r="D97" s="3" t="inlineStr">
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t>wt_eq%</t>
         </is>
       </c>
-      <c r="E97" s="3" t="inlineStr">
+      <c r="E98" s="3" t="inlineStr">
         <is>
           <t>Δwt_pp</t>
         </is>
       </c>
-      <c r="F97" s="3" t="inlineStr">
+      <c r="F98" s="3" t="inlineStr">
         <is>
           <t>value_Δ$</t>
         </is>
       </c>
-      <c r="G97" s="3" t="inlineStr">
+      <c r="G98" s="3" t="inlineStr">
         <is>
           <t>Trading_$</t>
         </is>
       </c>
-      <c r="H97" s="3" t="inlineStr">
+      <c r="H98" s="3" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="I97" s="3" t="inlineStr">
+      <c r="I98" s="3" t="inlineStr">
         <is>
           <t>also_in (other theses)</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>CRWV</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>COREWEAVE INC</t>
-        </is>
-      </c>
-      <c r="C98" s="4" t="n">
-        <v>211507071</v>
-      </c>
-      <c r="D98" s="5" t="n">
-        <v>0.03264913736443333</v>
-      </c>
-      <c r="E98" s="18" t="n">
-        <v>0.01735142756532645</v>
-      </c>
-      <c r="F98" s="7" t="n">
-        <v>148714925</v>
-      </c>
-      <c r="G98" s="7" t="n">
-        <v>130826417</v>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>Inference economics / token factories</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>NEBIUS GROUP N.V.</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>NEBIUS GROUP N.V.</t>
+          <t>WAYFAIR INC</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>17709401</v>
+        <v>77989541</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>0.002733698987731871</v>
+        <v>0.01346771089926284</v>
       </c>
       <c r="E99" s="18" t="n">
-        <v>0.001139435369604721</v>
-      </c>
-      <c r="F99" s="7" t="n">
-        <v>11165465</v>
-      </c>
-      <c r="G99" s="7" t="n">
-        <v>291912</v>
+        <v>-0.01275245303140551</v>
+      </c>
+      <c r="F99" s="6" t="n">
+        <v>-29635743</v>
+      </c>
+      <c r="G99" s="6" t="n">
+        <v>-54263201</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
+          <t>ACTIVE_TRIM</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ACVA</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ACV AUCTIONS INC</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="n">
+        <v>71204288</v>
+      </c>
+      <c r="D100" s="5" t="n">
+        <v>0.01229599191476008</v>
+      </c>
+      <c r="E100" s="18" t="n">
+        <v>0.00224059715364284</v>
+      </c>
+      <c r="F100" s="7" t="n">
+        <v>29930148</v>
+      </c>
+      <c r="G100" s="7" t="n">
+        <v>1213471</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="23" t="inlineStr">
-        <is>
-          <t>E-commerce   —   wt 2.3% (Q1 3.6%, Δ -1.3pp) · 2 held</t>
-        </is>
-      </c>
-      <c r="B101" s="24" t="n"/>
-      <c r="C101" s="24" t="n"/>
-      <c r="D101" s="24" t="n"/>
-      <c r="E101" s="24" t="n"/>
-      <c r="F101" s="24" t="n"/>
-      <c r="G101" s="24" t="n"/>
-      <c r="H101" s="24" t="n"/>
-      <c r="I101" s="24" t="n"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="inlineStr">
+      <c r="A102" s="23" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary   —   wt 1.8% (Q1 4.6%, Δ -2.8pp) · 2 held · 2 exited</t>
+        </is>
+      </c>
+      <c r="B102" s="24" t="n"/>
+      <c r="C102" s="24" t="n"/>
+      <c r="D102" s="24" t="n"/>
+      <c r="E102" s="24" t="n"/>
+      <c r="F102" s="24" t="n"/>
+      <c r="G102" s="24" t="n"/>
+      <c r="H102" s="24" t="n"/>
+      <c r="I102" s="24" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
         <is>
           <t>company</t>
         </is>
       </c>
-      <c r="C102" s="3" t="inlineStr">
+      <c r="C103" s="3" t="inlineStr">
         <is>
           <t>market_value</t>
         </is>
       </c>
-      <c r="D102" s="3" t="inlineStr">
+      <c r="D103" s="3" t="inlineStr">
         <is>
           <t>wt_eq%</t>
         </is>
       </c>
-      <c r="E102" s="3" t="inlineStr">
+      <c r="E103" s="3" t="inlineStr">
         <is>
           <t>Δwt_pp</t>
         </is>
       </c>
-      <c r="F102" s="3" t="inlineStr">
+      <c r="F103" s="3" t="inlineStr">
         <is>
           <t>value_Δ$</t>
         </is>
       </c>
-      <c r="G102" s="3" t="inlineStr">
+      <c r="G103" s="3" t="inlineStr">
         <is>
           <t>Trading_$</t>
         </is>
       </c>
-      <c r="H102" s="3" t="inlineStr">
+      <c r="H103" s="3" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="I102" s="3" t="inlineStr">
+      <c r="I103" s="3" t="inlineStr">
         <is>
           <t>also_in (other theses)</t>
         </is>
       </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>WAYFAIR INC</t>
-        </is>
-      </c>
-      <c r="C103" s="4" t="n">
-        <v>77989541</v>
-      </c>
-      <c r="D103" s="5" t="n">
-        <v>0.01203879957799664</v>
-      </c>
-      <c r="E103" s="18" t="n">
-        <v>-0.0141813643526717</v>
-      </c>
-      <c r="F103" s="6" t="n">
-        <v>-29635743</v>
-      </c>
-      <c r="G103" s="6" t="n">
-        <v>-54263201</v>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>ACTIVE_TRIM</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ACVA</t>
+          <t>DKS</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ACV AUCTIONS INC</t>
+          <t>DICKS SPORTING GOODS INC</t>
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>71204288</v>
+        <v>85080514</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>0.01099139886367521</v>
+        <v>0.01469222348305248</v>
       </c>
       <c r="E104" s="18" t="n">
-        <v>0.0009360041025579657</v>
-      </c>
-      <c r="F104" s="7" t="n">
-        <v>29930148</v>
-      </c>
-      <c r="G104" s="7" t="n">
-        <v>1213471</v>
+        <v>-0.007168787389891778</v>
+      </c>
+      <c r="F104" s="6" t="n">
+        <v>-4651858</v>
+      </c>
+      <c r="G104" s="6" t="n">
+        <v>-17558043</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
+          <t>ACTIVE_TRIM</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>WRBY</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>WARBY PARKER INC</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="n">
+        <v>21204717</v>
+      </c>
+      <c r="D105" s="5" t="n">
+        <v>0.00366176021290706</v>
+      </c>
+      <c r="E105" s="18" t="n">
+        <v>0.0001352981633949285</v>
+      </c>
+      <c r="F105" s="7" t="n">
+        <v>6729732</v>
+      </c>
+      <c r="G105" s="7" t="n">
+        <v>361289</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="23" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary   —   wt 1.6% (Q1 4.6%, Δ -3.0pp) · 2 held · 2 exited</t>
-        </is>
-      </c>
-      <c r="B106" s="24" t="n"/>
-      <c r="C106" s="24" t="n"/>
-      <c r="D106" s="24" t="n"/>
-      <c r="E106" s="24" t="n"/>
-      <c r="F106" s="24" t="n"/>
-      <c r="G106" s="24" t="n"/>
-      <c r="H106" s="24" t="n"/>
-      <c r="I106" s="24" t="n"/>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="18" t="n">
+        <v>-0.01079710977565713</v>
+      </c>
+      <c r="F106" s="6" t="n">
+        <v>-44318640</v>
+      </c>
+      <c r="G106" s="6" t="n">
+        <v>-44318640</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="inlineStr">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>WING</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="18" t="n">
+        <v>-0.01020515468454569</v>
+      </c>
+      <c r="F107" s="6" t="n">
+        <v>-41888856</v>
+      </c>
+      <c r="G107" s="6" t="n">
+        <v>-41888856</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="23" t="inlineStr">
+        <is>
+          <t>Fintech   —   wt 1.8% (Q1 4.2%, Δ -2.4pp) · 1 held · 2 exited</t>
+        </is>
+      </c>
+      <c r="B109" s="24" t="n"/>
+      <c r="C109" s="24" t="n"/>
+      <c r="D109" s="24" t="n"/>
+      <c r="E109" s="24" t="n"/>
+      <c r="F109" s="24" t="n"/>
+      <c r="G109" s="24" t="n"/>
+      <c r="H109" s="24" t="n"/>
+      <c r="I109" s="24" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="B107" s="3" t="inlineStr">
+      <c r="B110" s="3" t="inlineStr">
         <is>
           <t>company</t>
         </is>
       </c>
-      <c r="C107" s="3" t="inlineStr">
+      <c r="C110" s="3" t="inlineStr">
         <is>
           <t>market_value</t>
         </is>
       </c>
-      <c r="D107" s="3" t="inlineStr">
+      <c r="D110" s="3" t="inlineStr">
         <is>
           <t>wt_eq%</t>
         </is>
       </c>
-      <c r="E107" s="3" t="inlineStr">
+      <c r="E110" s="3" t="inlineStr">
         <is>
           <t>Δwt_pp</t>
         </is>
       </c>
-      <c r="F107" s="3" t="inlineStr">
+      <c r="F110" s="3" t="inlineStr">
         <is>
           <t>value_Δ$</t>
         </is>
       </c>
-      <c r="G107" s="3" t="inlineStr">
+      <c r="G110" s="3" t="inlineStr">
         <is>
           <t>Trading_$</t>
         </is>
       </c>
-      <c r="H107" s="3" t="inlineStr">
+      <c r="H110" s="3" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="I107" s="3" t="inlineStr">
+      <c r="I110" s="3" t="inlineStr">
         <is>
           <t>also_in (other theses)</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>DKS</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>DICKS SPORTING GOODS INC</t>
-        </is>
-      </c>
-      <c r="C108" s="4" t="n">
-        <v>85080514</v>
-      </c>
-      <c r="D108" s="5" t="n">
-        <v>0.01313339254091695</v>
-      </c>
-      <c r="E108" s="18" t="n">
-        <v>-0.008727618332027303</v>
-      </c>
-      <c r="F108" s="6" t="n">
-        <v>-4651858</v>
-      </c>
-      <c r="G108" s="6" t="n">
-        <v>-17558043</v>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>ACTIVE_TRIM</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>WRBY</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>WARBY PARKER INC</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="n">
-        <v>21204717</v>
-      </c>
-      <c r="D109" s="5" t="n">
-        <v>0.003273250935931758</v>
-      </c>
-      <c r="E109" s="18" t="n">
-        <v>-0.0002532111135803744</v>
-      </c>
-      <c r="F109" s="7" t="n">
-        <v>6729732</v>
-      </c>
-      <c r="G109" s="7" t="n">
-        <v>361289</v>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>RL</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr"/>
-      <c r="C110" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D110" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E110" s="18" t="n">
-        <v>-0.01079710977565713</v>
-      </c>
-      <c r="F110" s="6" t="n">
-        <v>-44318640</v>
-      </c>
-      <c r="G110" s="6" t="n">
-        <v>-44318640</v>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>EXIT</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>WING</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr"/>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>AFFIRM HLDGS INC</t>
+        </is>
+      </c>
       <c r="C111" s="4" t="n">
+        <v>103817228</v>
+      </c>
+      <c r="D111" s="5" t="n">
+        <v>0.01792779384439325</v>
+      </c>
+      <c r="E111" s="18" t="n">
+        <v>0.004591380752125989</v>
+      </c>
+      <c r="F111" s="7" t="n">
+        <v>49075570</v>
+      </c>
+      <c r="G111" s="7" t="n">
+        <v>6388545</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>RKT</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D111" s="5" t="n">
+      <c r="D112" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E111" s="18" t="n">
-        <v>-0.01020515468454569</v>
-      </c>
-      <c r="F111" s="6" t="n">
-        <v>-41888856</v>
-      </c>
-      <c r="G111" s="6" t="n">
-        <v>-41888856</v>
-      </c>
-      <c r="H111" t="inlineStr">
+      <c r="E112" s="18" t="n">
+        <v>-0.02122895688237866</v>
+      </c>
+      <c r="F112" s="6" t="n">
+        <v>-87137995</v>
+      </c>
+      <c r="G112" s="6" t="n">
+        <v>-87137995</v>
+      </c>
+      <c r="H112" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="23" t="inlineStr">
-        <is>
-          <t>Fintech   —   wt 1.6% (Q1 4.2%, Δ -2.6pp) · 1 held · 2 exited</t>
-        </is>
-      </c>
-      <c r="B113" s="24" t="n"/>
-      <c r="C113" s="24" t="n"/>
-      <c r="D113" s="24" t="n"/>
-      <c r="E113" s="24" t="n"/>
-      <c r="F113" s="24" t="n"/>
-      <c r="G113" s="24" t="n"/>
-      <c r="H113" s="24" t="n"/>
-      <c r="I113" s="24" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="3" t="inlineStr">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>CHYM</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="18" t="n">
+        <v>-0.007404678516223557</v>
+      </c>
+      <c r="F113" s="6" t="n">
+        <v>-30393808</v>
+      </c>
+      <c r="G113" s="6" t="n">
+        <v>-30393808</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="23" t="inlineStr">
+        <is>
+          <t>AI/Datacenter Power   —   wt 1.8% (Q1 1.9%, Δ -0.2pp) · 3 held · 1 exited</t>
+        </is>
+      </c>
+      <c r="B115" s="24" t="n"/>
+      <c r="C115" s="24" t="n"/>
+      <c r="D115" s="24" t="n"/>
+      <c r="E115" s="24" t="n"/>
+      <c r="F115" s="24" t="n"/>
+      <c r="G115" s="24" t="n"/>
+      <c r="H115" s="24" t="n"/>
+      <c r="I115" s="24" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="B114" s="3" t="inlineStr">
+      <c r="B116" s="3" t="inlineStr">
         <is>
           <t>company</t>
         </is>
       </c>
-      <c r="C114" s="3" t="inlineStr">
+      <c r="C116" s="3" t="inlineStr">
         <is>
           <t>market_value</t>
         </is>
       </c>
-      <c r="D114" s="3" t="inlineStr">
+      <c r="D116" s="3" t="inlineStr">
         <is>
           <t>wt_eq%</t>
         </is>
       </c>
-      <c r="E114" s="3" t="inlineStr">
+      <c r="E116" s="3" t="inlineStr">
         <is>
           <t>Δwt_pp</t>
         </is>
       </c>
-      <c r="F114" s="3" t="inlineStr">
+      <c r="F116" s="3" t="inlineStr">
         <is>
           <t>value_Δ$</t>
         </is>
       </c>
-      <c r="G114" s="3" t="inlineStr">
+      <c r="G116" s="3" t="inlineStr">
         <is>
           <t>Trading_$</t>
         </is>
       </c>
-      <c r="H114" s="3" t="inlineStr">
+      <c r="H116" s="3" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="I114" s="3" t="inlineStr">
+      <c r="I116" s="3" t="inlineStr">
         <is>
           <t>also_in (other theses)</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>AFRM</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>AFFIRM HLDGS INC</t>
-        </is>
-      </c>
-      <c r="C115" s="4" t="n">
-        <v>103817228</v>
-      </c>
-      <c r="D115" s="5" t="n">
-        <v>0.01602567196331084</v>
-      </c>
-      <c r="E115" s="18" t="n">
-        <v>0.002689258871043576</v>
-      </c>
-      <c r="F115" s="7" t="n">
-        <v>49075570</v>
-      </c>
-      <c r="G115" s="7" t="n">
-        <v>6388545</v>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>RKT</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr"/>
-      <c r="C116" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D116" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" s="18" t="n">
-        <v>-0.02122895688237866</v>
-      </c>
-      <c r="F116" s="6" t="n">
-        <v>-87137995</v>
-      </c>
-      <c r="G116" s="6" t="n">
-        <v>-87137995</v>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>EXIT</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CHYM</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr"/>
+          <t>CIFR</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>CIPHER DIGITAL INC</t>
+        </is>
+      </c>
       <c r="C117" s="4" t="n">
+        <v>87867021</v>
+      </c>
+      <c r="D117" s="5" t="n">
+        <v>0.01517341455320857</v>
+      </c>
+      <c r="E117" s="18" t="n">
+        <v>0.01517341455320857</v>
+      </c>
+      <c r="F117" s="7" t="n">
+        <v>87867021</v>
+      </c>
+      <c r="G117" s="7" t="n">
+        <v>87867021</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>INNIO NV</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>INNIO NV</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="n">
+        <v>13790927</v>
+      </c>
+      <c r="D118" s="5" t="n">
+        <v>0.002381501615310675</v>
+      </c>
+      <c r="E118" s="18" t="n">
+        <v>0.002381501615310675</v>
+      </c>
+      <c r="F118" s="7" t="n">
+        <v>13790927</v>
+      </c>
+      <c r="G118" s="7" t="n">
+        <v>13790927</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>FRVO</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>FERVO ENERGY CO</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="n">
+        <v>291102</v>
+      </c>
+      <c r="D119" s="5" t="n">
+        <v>5.026927364782426e-05</v>
+      </c>
+      <c r="E119" s="18" t="n">
+        <v>5.026927364782426e-05</v>
+      </c>
+      <c r="F119" s="7" t="n">
+        <v>291102</v>
+      </c>
+      <c r="G119" s="7" t="n">
+        <v>291102</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D117" s="5" t="n">
+      <c r="D120" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E117" s="18" t="n">
-        <v>-0.007404678516223557</v>
-      </c>
-      <c r="F117" s="6" t="n">
-        <v>-30393808</v>
-      </c>
-      <c r="G117" s="6" t="n">
-        <v>-30393808</v>
-      </c>
-      <c r="H117" t="inlineStr">
+      <c r="E120" s="18" t="n">
+        <v>-0.01918325473661888</v>
+      </c>
+      <c r="F120" s="6" t="n">
+        <v>-78741050</v>
+      </c>
+      <c r="G120" s="6" t="n">
+        <v>-78741050</v>
+      </c>
+      <c r="H120" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="23" t="inlineStr">
-        <is>
-          <t>AI/Datacenter Power   —   wt 1.6% (Q1 1.9%, Δ -0.3pp) · 3 held · 1 exited</t>
-        </is>
-      </c>
-      <c r="B119" s="24" t="n"/>
-      <c r="C119" s="24" t="n"/>
-      <c r="D119" s="24" t="n"/>
-      <c r="E119" s="24" t="n"/>
-      <c r="F119" s="24" t="n"/>
-      <c r="G119" s="24" t="n"/>
-      <c r="H119" s="24" t="n"/>
-      <c r="I119" s="24" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="3" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="23" t="inlineStr">
+        <is>
+          <t>Semiconductor Supply Chain   —   wt 1.7% (Q1 2.0%, Δ -0.4pp) · 3 held · 1 exited</t>
+        </is>
+      </c>
+      <c r="B122" s="24" t="n"/>
+      <c r="C122" s="24" t="n"/>
+      <c r="D122" s="24" t="n"/>
+      <c r="E122" s="24" t="n"/>
+      <c r="F122" s="24" t="n"/>
+      <c r="G122" s="24" t="n"/>
+      <c r="H122" s="24" t="n"/>
+      <c r="I122" s="24" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="B120" s="3" t="inlineStr">
+      <c r="B123" s="3" t="inlineStr">
         <is>
           <t>company</t>
         </is>
       </c>
-      <c r="C120" s="3" t="inlineStr">
+      <c r="C123" s="3" t="inlineStr">
         <is>
           <t>market_value</t>
         </is>
       </c>
-      <c r="D120" s="3" t="inlineStr">
+      <c r="D123" s="3" t="inlineStr">
         <is>
           <t>wt_eq%</t>
         </is>
       </c>
-      <c r="E120" s="3" t="inlineStr">
+      <c r="E123" s="3" t="inlineStr">
         <is>
           <t>Δwt_pp</t>
         </is>
       </c>
-      <c r="F120" s="3" t="inlineStr">
+      <c r="F123" s="3" t="inlineStr">
         <is>
           <t>value_Δ$</t>
         </is>
       </c>
-      <c r="G120" s="3" t="inlineStr">
+      <c r="G123" s="3" t="inlineStr">
         <is>
           <t>Trading_$</t>
         </is>
       </c>
-      <c r="H120" s="3" t="inlineStr">
+      <c r="H123" s="3" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="I120" s="3" t="inlineStr">
+      <c r="I123" s="3" t="inlineStr">
         <is>
           <t>also_in (other theses)</t>
         </is>
       </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>CIFR</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>CIPHER DIGITAL INC</t>
-        </is>
-      </c>
-      <c r="C121" s="4" t="n">
-        <v>87867021</v>
-      </c>
-      <c r="D121" s="5" t="n">
-        <v>0.0135635296960476</v>
-      </c>
-      <c r="E121" s="18" t="n">
-        <v>0.0135635296960476</v>
-      </c>
-      <c r="F121" s="7" t="n">
-        <v>87867021</v>
-      </c>
-      <c r="G121" s="7" t="n">
-        <v>87867021</v>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>INNIO NV</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>INNIO NV</t>
-        </is>
-      </c>
-      <c r="C122" s="4" t="n">
-        <v>13790927</v>
-      </c>
-      <c r="D122" s="5" t="n">
-        <v>0.002128826558266094</v>
-      </c>
-      <c r="E122" s="18" t="n">
-        <v>0.002128826558266094</v>
-      </c>
-      <c r="F122" s="7" t="n">
-        <v>13790927</v>
-      </c>
-      <c r="G122" s="7" t="n">
-        <v>13790927</v>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>FRVO</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>FERVO ENERGY CO</t>
-        </is>
-      </c>
-      <c r="C123" s="4" t="n">
-        <v>291102</v>
-      </c>
-      <c r="D123" s="5" t="n">
-        <v>4.493575150998744e-05</v>
-      </c>
-      <c r="E123" s="18" t="n">
-        <v>4.493575150998744e-05</v>
-      </c>
-      <c r="F123" s="7" t="n">
-        <v>291102</v>
-      </c>
-      <c r="G123" s="7" t="n">
-        <v>291102</v>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>VST</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr"/>
+          <t>PDFS</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>PDF SOLUTIONS INC</t>
+        </is>
+      </c>
       <c r="C124" s="4" t="n">
+        <v>46617763</v>
+      </c>
+      <c r="D124" s="5" t="n">
+        <v>0.00805024041434417</v>
+      </c>
+      <c r="E124" s="18" t="n">
+        <v>0.00805024041434417</v>
+      </c>
+      <c r="F124" s="7" t="n">
+        <v>46617763</v>
+      </c>
+      <c r="G124" s="7" t="n">
+        <v>46617763</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>ROG</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>ROGERS CORP</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="n">
+        <v>30995890</v>
+      </c>
+      <c r="D125" s="5" t="n">
+        <v>0.005352559846266461</v>
+      </c>
+      <c r="E125" s="18" t="n">
+        <v>0.0004867673177583348</v>
+      </c>
+      <c r="F125" s="7" t="n">
+        <v>11023387</v>
+      </c>
+      <c r="G125" s="7" t="n">
+        <v>528193</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>VECO</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>VEECO INSTRS INC DEL</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="n">
+        <v>18034260</v>
+      </c>
+      <c r="D126" s="5" t="n">
+        <v>0.003114266308634125</v>
+      </c>
+      <c r="E126" s="18" t="n">
+        <v>0.001184605470808496</v>
+      </c>
+      <c r="F126" s="7" t="n">
+        <v>10113627</v>
+      </c>
+      <c r="G126" s="7" t="n">
+        <v>302897</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>SNPS</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D124" s="5" t="n">
+      <c r="D127" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E124" s="18" t="n">
-        <v>-0.01918325473661888</v>
-      </c>
-      <c r="F124" s="6" t="n">
-        <v>-78741050</v>
-      </c>
-      <c r="G124" s="6" t="n">
-        <v>-78741050</v>
-      </c>
-      <c r="H124" t="inlineStr">
+      <c r="E127" s="18" t="n">
+        <v>-0.01322589670241481</v>
+      </c>
+      <c r="F127" s="6" t="n">
+        <v>-54288024</v>
+      </c>
+      <c r="G127" s="6" t="n">
+        <v>-54288024</v>
+      </c>
+      <c r="H127" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="23" t="inlineStr">
-        <is>
-          <t>Semiconductor Supply Chain   —   wt 1.5% (Q1 2.0%, Δ -0.5pp) · 3 held · 1 exited</t>
-        </is>
-      </c>
-      <c r="B126" s="24" t="n"/>
-      <c r="C126" s="24" t="n"/>
-      <c r="D126" s="24" t="n"/>
-      <c r="E126" s="24" t="n"/>
-      <c r="F126" s="24" t="n"/>
-      <c r="G126" s="24" t="n"/>
-      <c r="H126" s="24" t="n"/>
-      <c r="I126" s="24" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="3" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="23" t="inlineStr">
+        <is>
+          <t>Semiconductor Manufacturing   —   wt 1.6% (Q1 1.2%, Δ +0.4pp) · 1 held · 1 exited</t>
+        </is>
+      </c>
+      <c r="B129" s="24" t="n"/>
+      <c r="C129" s="24" t="n"/>
+      <c r="D129" s="24" t="n"/>
+      <c r="E129" s="24" t="n"/>
+      <c r="F129" s="24" t="n"/>
+      <c r="G129" s="24" t="n"/>
+      <c r="H129" s="24" t="n"/>
+      <c r="I129" s="24" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="B127" s="3" t="inlineStr">
+      <c r="B130" s="3" t="inlineStr">
         <is>
           <t>company</t>
         </is>
       </c>
-      <c r="C127" s="3" t="inlineStr">
+      <c r="C130" s="3" t="inlineStr">
         <is>
           <t>market_value</t>
         </is>
       </c>
-      <c r="D127" s="3" t="inlineStr">
+      <c r="D130" s="3" t="inlineStr">
         <is>
           <t>wt_eq%</t>
         </is>
       </c>
-      <c r="E127" s="3" t="inlineStr">
+      <c r="E130" s="3" t="inlineStr">
         <is>
           <t>Δwt_pp</t>
         </is>
       </c>
-      <c r="F127" s="3" t="inlineStr">
+      <c r="F130" s="3" t="inlineStr">
         <is>
           <t>value_Δ$</t>
         </is>
       </c>
-      <c r="G127" s="3" t="inlineStr">
+      <c r="G130" s="3" t="inlineStr">
         <is>
           <t>Trading_$</t>
         </is>
       </c>
-      <c r="H127" s="3" t="inlineStr">
+      <c r="H130" s="3" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="I127" s="3" t="inlineStr">
+      <c r="I130" s="3" t="inlineStr">
         <is>
           <t>also_in (other theses)</t>
         </is>
       </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>PDFS</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>PDF SOLUTIONS INC</t>
-        </is>
-      </c>
-      <c r="C128" s="4" t="n">
-        <v>46617763</v>
-      </c>
-      <c r="D128" s="5" t="n">
-        <v>0.007196117560578376</v>
-      </c>
-      <c r="E128" s="18" t="n">
-        <v>0.007196117560578376</v>
-      </c>
-      <c r="F128" s="7" t="n">
-        <v>46617763</v>
-      </c>
-      <c r="G128" s="7" t="n">
-        <v>46617763</v>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>ROG</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>ROGERS CORP</t>
-        </is>
-      </c>
-      <c r="C129" s="4" t="n">
-        <v>30995890</v>
-      </c>
-      <c r="D129" s="5" t="n">
-        <v>0.004784658335809801</v>
-      </c>
-      <c r="E129" s="18" t="n">
-        <v>-8.113419269832556e-05</v>
-      </c>
-      <c r="F129" s="7" t="n">
-        <v>11023387</v>
-      </c>
-      <c r="G129" s="7" t="n">
-        <v>528193</v>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>VECO</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>VEECO INSTRS INC DEL</t>
-        </is>
-      </c>
-      <c r="C130" s="4" t="n">
-        <v>18034260</v>
-      </c>
-      <c r="D130" s="5" t="n">
-        <v>0.002783845614343103</v>
-      </c>
-      <c r="E130" s="18" t="n">
-        <v>0.0008541847765174734</v>
-      </c>
-      <c r="F130" s="7" t="n">
-        <v>10113627</v>
-      </c>
-      <c r="G130" s="7" t="n">
-        <v>302897</v>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SNPS</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>INTEL CORP</t>
+        </is>
+      </c>
       <c r="C131" s="4" t="n">
+        <v>92686673</v>
+      </c>
+      <c r="D131" s="5" t="n">
+        <v>0.01600570153603687</v>
+      </c>
+      <c r="E131" s="18" t="n">
+        <v>0.008976684072802318</v>
+      </c>
+      <c r="F131" s="7" t="n">
+        <v>63834832</v>
+      </c>
+      <c r="G131" s="7" t="n">
+        <v>1397696</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Intel recovery / foundry failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>G39387108</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
+      <c r="C132" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D131" s="5" t="n">
+      <c r="D132" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E131" s="18" t="n">
-        <v>-0.01322589670241481</v>
-      </c>
-      <c r="F131" s="6" t="n">
-        <v>-54288024</v>
-      </c>
-      <c r="G131" s="6" t="n">
-        <v>-54288024</v>
-      </c>
-      <c r="H131" t="inlineStr">
+      <c r="E132" s="18" t="n">
+        <v>-0.005142889656853531</v>
+      </c>
+      <c r="F132" s="6" t="n">
+        <v>-21109897</v>
+      </c>
+      <c r="G132" s="6" t="n">
+        <v>-21109897</v>
+      </c>
+      <c r="H132" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="23" t="inlineStr">
-        <is>
-          <t>Semiconductor Manufacturing   —   wt 1.4% (Q1 1.2%, Δ +0.2pp) · 1 held · 1 exited</t>
-        </is>
-      </c>
-      <c r="B133" s="24" t="n"/>
-      <c r="C133" s="24" t="n"/>
-      <c r="D133" s="24" t="n"/>
-      <c r="E133" s="24" t="n"/>
-      <c r="F133" s="24" t="n"/>
-      <c r="G133" s="24" t="n"/>
-      <c r="H133" s="24" t="n"/>
-      <c r="I133" s="24" t="n"/>
-    </row>
     <row r="134">
-      <c r="A134" s="3" t="inlineStr">
+      <c r="A134" s="23" t="inlineStr">
+        <is>
+          <t>Humanoid robotics / Tesla Optimus   —   wt 1.5% (Q1 1.8%, Δ -0.3pp) · 1 held</t>
+        </is>
+      </c>
+      <c r="B134" s="24" t="n"/>
+      <c r="C134" s="24" t="n"/>
+      <c r="D134" s="24" t="n"/>
+      <c r="E134" s="24" t="n"/>
+      <c r="F134" s="24" t="n"/>
+      <c r="G134" s="24" t="n"/>
+      <c r="H134" s="24" t="n"/>
+      <c r="I134" s="24" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="B134" s="3" t="inlineStr">
+      <c r="B135" s="3" t="inlineStr">
         <is>
           <t>company</t>
         </is>
       </c>
-      <c r="C134" s="3" t="inlineStr">
+      <c r="C135" s="3" t="inlineStr">
         <is>
           <t>market_value</t>
         </is>
       </c>
-      <c r="D134" s="3" t="inlineStr">
+      <c r="D135" s="3" t="inlineStr">
         <is>
           <t>wt_eq%</t>
         </is>
       </c>
-      <c r="E134" s="3" t="inlineStr">
+      <c r="E135" s="3" t="inlineStr">
         <is>
           <t>Δwt_pp</t>
         </is>
       </c>
-      <c r="F134" s="3" t="inlineStr">
+      <c r="F135" s="3" t="inlineStr">
         <is>
           <t>value_Δ$</t>
         </is>
       </c>
-      <c r="G134" s="3" t="inlineStr">
+      <c r="G135" s="3" t="inlineStr">
         <is>
           <t>Trading_$</t>
         </is>
       </c>
-      <c r="H134" s="3" t="inlineStr">
+      <c r="H135" s="3" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="I134" s="3" t="inlineStr">
+      <c r="I135" s="3" t="inlineStr">
         <is>
           <t>also_in (other theses)</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>INTC</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>INTEL CORP</t>
-        </is>
-      </c>
-      <c r="C135" s="4" t="n">
-        <v>92686673</v>
-      </c>
-      <c r="D135" s="5" t="n">
-        <v>0.01430751182133913</v>
-      </c>
-      <c r="E135" s="18" t="n">
-        <v>0.007278494358104575</v>
-      </c>
-      <c r="F135" s="7" t="n">
-        <v>63834832</v>
-      </c>
-      <c r="G135" s="7" t="n">
-        <v>1397696</v>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>Intel recovery / foundry failure</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>G39387108</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr"/>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>TESLA INC</t>
+        </is>
+      </c>
       <c r="C136" s="4" t="n">
-        <v>0</v>
+        <v>85918065</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>0</v>
+        <v>0.01483685691192967</v>
       </c>
       <c r="E136" s="18" t="n">
-        <v>-0.005142889656853531</v>
-      </c>
-      <c r="F136" s="6" t="n">
-        <v>-21109897</v>
-      </c>
-      <c r="G136" s="6" t="n">
-        <v>-21109897</v>
+        <v>-0.003348631190600439</v>
+      </c>
+      <c r="F136" s="7" t="n">
+        <v>11272524</v>
+      </c>
+      <c r="G136" s="7" t="n">
+        <v>1463688</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>EXIT</t>
+          <t>DRIFT_DOWN</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Tesla / EV / FSD</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="23" t="inlineStr">
         <is>
-          <t>Humanoid robotics / Tesla Optimus   —   wt 1.3% (Q1 1.8%, Δ -0.5pp) · 1 held</t>
+          <t>Industrial IoT   —   wt 1.3% (Q1 0.0%, Δ +1.3pp) · 1 held</t>
         </is>
       </c>
       <c r="B138" s="24" t="n"/>
@@ -28303,44 +28239,40 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>IOT</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>TESLA INC</t>
+          <t>SAMSARA INC</t>
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>85918065</v>
+        <v>74869487</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>0.01326268050050824</v>
+        <v>0.01292892089327872</v>
       </c>
       <c r="E140" s="18" t="n">
-        <v>-0.004922807602021877</v>
+        <v>0.01292892089327872</v>
       </c>
       <c r="F140" s="7" t="n">
-        <v>11272524</v>
+        <v>74869487</v>
       </c>
       <c r="G140" s="7" t="n">
-        <v>1463688</v>
+        <v>74869487</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>DRIFT_DOWN</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>Tesla / EV / FSD</t>
-        </is>
-      </c>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="23" t="inlineStr">
         <is>
-          <t>Industrial IoT   —   wt 1.2% (Q1 0.0%, Δ +1.2pp) · 1 held</t>
+          <t>Real Estate   —   wt 1.2% (Q1 1.0%, Δ +0.2pp) · 1 held</t>
         </is>
       </c>
       <c r="B142" s="24" t="n"/>
@@ -28402,32 +28334,32 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>IOT</t>
+          <t>COMP</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SAMSARA INC</t>
+          <t>COMPASS INC</t>
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>74869487</v>
+        <v>69768331</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>0.01155717467936405</v>
+        <v>0.01204802207814093</v>
       </c>
       <c r="E144" s="18" t="n">
-        <v>0.01155717467936405</v>
+        <v>0.002142684218807435</v>
       </c>
       <c r="F144" s="7" t="n">
-        <v>74869487</v>
+        <v>29110126</v>
       </c>
       <c r="G144" s="7" t="n">
-        <v>74869487</v>
+        <v>1188896</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -28435,7 +28367,7 @@
     <row r="146">
       <c r="A146" s="23" t="inlineStr">
         <is>
-          <t>Real Estate   —   wt 1.1% (Q1 1.0%, Δ +0.1pp) · 1 held</t>
+          <t>Web / SMB SaaS   —   wt 1.1% (Q1 1.4%, Δ -0.3pp) · 1 held</t>
         </is>
       </c>
       <c r="B146" s="24" t="n"/>
@@ -28497,28 +28429,28 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>COMP</t>
+          <t>WIX COM LTD</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>COMPASS INC</t>
+          <t>WIX COM LTD</t>
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>69768331</v>
+        <v>66170239</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>0.01076973839095078</v>
+        <v>0.01142668154678749</v>
       </c>
       <c r="E148" s="18" t="n">
-        <v>0.0008644005316172853</v>
+        <v>-0.002845525447767374</v>
       </c>
       <c r="F148" s="7" t="n">
-        <v>29110126</v>
+        <v>7587450</v>
       </c>
       <c r="G148" s="7" t="n">
-        <v>1188896</v>
+        <v>36660956</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -28530,7 +28462,7 @@
     <row r="150">
       <c r="A150" s="23" t="inlineStr">
         <is>
-          <t>Web / SMB SaaS   —   wt 1.0% (Q1 1.4%, Δ -0.4pp) · 1 held</t>
+          <t>Payments   —   wt 0.8% (Q1 1.1%, Δ -0.3pp) · 1 held · 1 exited</t>
         </is>
       </c>
       <c r="B150" s="24" t="n"/>
@@ -28592,283 +28524,283 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>WIX COM LTD</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>WIX COM LTD</t>
+          <t>MASTERCARD INCORPORATED</t>
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>66170239</v>
+        <v>48087854</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>0.01021432149920124</v>
+        <v>0.008304104718836079</v>
       </c>
       <c r="E152" s="18" t="n">
-        <v>-0.004057885495353626</v>
+        <v>0.002265836771094864</v>
       </c>
       <c r="F152" s="7" t="n">
-        <v>7587450</v>
+        <v>23302719</v>
       </c>
       <c r="G152" s="7" t="n">
-        <v>36660956</v>
+        <v>22611240</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="23" t="inlineStr">
-        <is>
-          <t>Payments   —   wt 0.7% (Q1 1.1%, Δ -0.4pp) · 1 held · 1 exited</t>
-        </is>
-      </c>
-      <c r="B154" s="24" t="n"/>
-      <c r="C154" s="24" t="n"/>
-      <c r="D154" s="24" t="n"/>
-      <c r="E154" s="24" t="n"/>
-      <c r="F154" s="24" t="n"/>
-      <c r="G154" s="24" t="n"/>
-      <c r="H154" s="24" t="n"/>
-      <c r="I154" s="24" t="n"/>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Stablecoin / Visa-MC disruption</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" s="18" t="n">
+        <v>-0.005275148321783207</v>
+      </c>
+      <c r="F153" s="6" t="n">
+        <v>-21652776</v>
+      </c>
+      <c r="G153" s="6" t="n">
+        <v>-21652776</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
     </row>
     <row r="155">
-      <c r="A155" s="3" t="inlineStr">
+      <c r="A155" s="23" t="inlineStr">
+        <is>
+          <t>Construction   —   wt 0.7% (Q1 0.9%, Δ -0.3pp) · 2 held</t>
+        </is>
+      </c>
+      <c r="B155" s="24" t="n"/>
+      <c r="C155" s="24" t="n"/>
+      <c r="D155" s="24" t="n"/>
+      <c r="E155" s="24" t="n"/>
+      <c r="F155" s="24" t="n"/>
+      <c r="G155" s="24" t="n"/>
+      <c r="H155" s="24" t="n"/>
+      <c r="I155" s="24" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="B155" s="3" t="inlineStr">
+      <c r="B156" s="3" t="inlineStr">
         <is>
           <t>company</t>
         </is>
       </c>
-      <c r="C155" s="3" t="inlineStr">
+      <c r="C156" s="3" t="inlineStr">
         <is>
           <t>market_value</t>
         </is>
       </c>
-      <c r="D155" s="3" t="inlineStr">
+      <c r="D156" s="3" t="inlineStr">
         <is>
           <t>wt_eq%</t>
         </is>
       </c>
-      <c r="E155" s="3" t="inlineStr">
+      <c r="E156" s="3" t="inlineStr">
         <is>
           <t>Δwt_pp</t>
         </is>
       </c>
-      <c r="F155" s="3" t="inlineStr">
+      <c r="F156" s="3" t="inlineStr">
         <is>
           <t>value_Δ$</t>
         </is>
       </c>
-      <c r="G155" s="3" t="inlineStr">
+      <c r="G156" s="3" t="inlineStr">
         <is>
           <t>Trading_$</t>
         </is>
       </c>
-      <c r="H155" s="3" t="inlineStr">
+      <c r="H156" s="3" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="I155" s="3" t="inlineStr">
+      <c r="I156" s="3" t="inlineStr">
         <is>
           <t>also_in (other theses)</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>MASTERCARD INCORPORATED</t>
-        </is>
-      </c>
-      <c r="C156" s="4" t="n">
-        <v>48087854</v>
-      </c>
-      <c r="D156" s="5" t="n">
-        <v>0.007423047103738744</v>
-      </c>
-      <c r="E156" s="18" t="n">
-        <v>0.001384779155997529</v>
-      </c>
-      <c r="F156" s="7" t="n">
-        <v>23302719</v>
-      </c>
-      <c r="G156" s="7" t="n">
-        <v>22611240</v>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Stablecoin / Visa-MC disruption</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr"/>
+          <t>FERG</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>FERGUSON ENTERPRISES INC</t>
+        </is>
+      </c>
       <c r="C157" s="4" t="n">
-        <v>0</v>
+        <v>35067643</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>0</v>
+        <v>0.006055695055860864</v>
       </c>
       <c r="E157" s="18" t="n">
-        <v>-0.005275148321783207</v>
-      </c>
-      <c r="F157" s="6" t="n">
-        <v>-21652776</v>
-      </c>
-      <c r="G157" s="6" t="n">
-        <v>-21652776</v>
+        <v>-0.002261347500151259</v>
+      </c>
+      <c r="F157" s="7" t="n">
+        <v>928876</v>
+      </c>
+      <c r="G157" s="7" t="n">
+        <v>333211</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="23" t="inlineStr">
-        <is>
-          <t>Construction   —   wt 0.6% (Q1 0.9%, Δ -0.3pp) · 2 held</t>
-        </is>
-      </c>
-      <c r="B159" s="24" t="n"/>
-      <c r="C159" s="24" t="n"/>
-      <c r="D159" s="24" t="n"/>
-      <c r="E159" s="24" t="n"/>
-      <c r="F159" s="24" t="n"/>
-      <c r="G159" s="24" t="n"/>
-      <c r="H159" s="24" t="n"/>
-      <c r="I159" s="24" t="n"/>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>EQPT</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>EQUIPMENTSHARE COM INC</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="n">
+        <v>4268795</v>
+      </c>
+      <c r="D158" s="5" t="n">
+        <v>0.0007371616272009947</v>
+      </c>
+      <c r="E158" s="18" t="n">
+        <v>-0.0003220178894186357</v>
+      </c>
+      <c r="F158" s="6" t="n">
+        <v>-78794</v>
+      </c>
+      <c r="G158" s="7" t="n">
+        <v>72742</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="3" t="inlineStr">
+      <c r="A160" s="23" t="inlineStr">
+        <is>
+          <t>Telecom   —   wt 0.6% (Q1 3.3%, Δ -2.8pp) · 1 held · 1 exited</t>
+        </is>
+      </c>
+      <c r="B160" s="24" t="n"/>
+      <c r="C160" s="24" t="n"/>
+      <c r="D160" s="24" t="n"/>
+      <c r="E160" s="24" t="n"/>
+      <c r="F160" s="24" t="n"/>
+      <c r="G160" s="24" t="n"/>
+      <c r="H160" s="24" t="n"/>
+      <c r="I160" s="24" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="B160" s="3" t="inlineStr">
+      <c r="B161" s="3" t="inlineStr">
         <is>
           <t>company</t>
         </is>
       </c>
-      <c r="C160" s="3" t="inlineStr">
+      <c r="C161" s="3" t="inlineStr">
         <is>
           <t>market_value</t>
         </is>
       </c>
-      <c r="D160" s="3" t="inlineStr">
+      <c r="D161" s="3" t="inlineStr">
         <is>
           <t>wt_eq%</t>
         </is>
       </c>
-      <c r="E160" s="3" t="inlineStr">
+      <c r="E161" s="3" t="inlineStr">
         <is>
           <t>Δwt_pp</t>
         </is>
       </c>
-      <c r="F160" s="3" t="inlineStr">
+      <c r="F161" s="3" t="inlineStr">
         <is>
           <t>value_Δ$</t>
         </is>
       </c>
-      <c r="G160" s="3" t="inlineStr">
+      <c r="G161" s="3" t="inlineStr">
         <is>
           <t>Trading_$</t>
         </is>
       </c>
-      <c r="H160" s="3" t="inlineStr">
+      <c r="H161" s="3" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="I160" s="3" t="inlineStr">
+      <c r="I161" s="3" t="inlineStr">
         <is>
           <t>also_in (other theses)</t>
         </is>
       </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>FERG</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>FERGUSON ENTERPRISES INC</t>
-        </is>
-      </c>
-      <c r="C161" s="4" t="n">
-        <v>35067643</v>
-      </c>
-      <c r="D161" s="5" t="n">
-        <v>0.005413191568209599</v>
-      </c>
-      <c r="E161" s="18" t="n">
-        <v>-0.002903850987802524</v>
-      </c>
-      <c r="F161" s="7" t="n">
-        <v>928876</v>
-      </c>
-      <c r="G161" s="7" t="n">
-        <v>333211</v>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>EQPT</t>
+          <t>NOK</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EQUIPMENTSHARE COM INC</t>
+          <t>NOKIA CORP</t>
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>4268795</v>
+        <v>33531655</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>0.0006589494794507658</v>
+        <v>0.00579045125440373</v>
       </c>
       <c r="E162" s="18" t="n">
-        <v>-0.0004002300371688646</v>
-      </c>
-      <c r="F162" s="6" t="n">
-        <v>-78794</v>
+        <v>0.0009289584559963143</v>
+      </c>
+      <c r="F162" s="7" t="n">
+        <v>13576801</v>
       </c>
       <c r="G162" s="7" t="n">
-        <v>72742</v>
+        <v>571399</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -28877,133 +28809,133 @@
       </c>
       <c r="I162" t="inlineStr"/>
     </row>
-    <row r="164">
-      <c r="A164" s="23" t="inlineStr">
-        <is>
-          <t>Telecom   —   wt 0.5% (Q1 3.3%, Δ -2.8pp) · 1 held · 1 exited</t>
-        </is>
-      </c>
-      <c r="B164" s="24" t="n"/>
-      <c r="C164" s="24" t="n"/>
-      <c r="D164" s="24" t="n"/>
-      <c r="E164" s="24" t="n"/>
-      <c r="F164" s="24" t="n"/>
-      <c r="G164" s="24" t="n"/>
-      <c r="H164" s="24" t="n"/>
-      <c r="I164" s="24" t="n"/>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>SATS</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D163" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" s="18" t="n">
+        <v>-0.02853099709658855</v>
+      </c>
+      <c r="F163" s="6" t="n">
+        <v>-117110506</v>
+      </c>
+      <c r="G163" s="6" t="n">
+        <v>-117110506</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
     </row>
     <row r="165">
-      <c r="A165" s="3" t="inlineStr">
+      <c r="A165" s="23" t="inlineStr">
+        <is>
+          <t>Healthcare/Diagnostics   —   wt 0.5% (Q1 0.0%, Δ +0.5pp) · 1 held</t>
+        </is>
+      </c>
+      <c r="B165" s="24" t="n"/>
+      <c r="C165" s="24" t="n"/>
+      <c r="D165" s="24" t="n"/>
+      <c r="E165" s="24" t="n"/>
+      <c r="F165" s="24" t="n"/>
+      <c r="G165" s="24" t="n"/>
+      <c r="H165" s="24" t="n"/>
+      <c r="I165" s="24" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
       </c>
-      <c r="B165" s="3" t="inlineStr">
+      <c r="B166" s="3" t="inlineStr">
         <is>
           <t>company</t>
         </is>
       </c>
-      <c r="C165" s="3" t="inlineStr">
+      <c r="C166" s="3" t="inlineStr">
         <is>
           <t>market_value</t>
         </is>
       </c>
-      <c r="D165" s="3" t="inlineStr">
+      <c r="D166" s="3" t="inlineStr">
         <is>
           <t>wt_eq%</t>
         </is>
       </c>
-      <c r="E165" s="3" t="inlineStr">
+      <c r="E166" s="3" t="inlineStr">
         <is>
           <t>Δwt_pp</t>
         </is>
       </c>
-      <c r="F165" s="3" t="inlineStr">
+      <c r="F166" s="3" t="inlineStr">
         <is>
           <t>value_Δ$</t>
         </is>
       </c>
-      <c r="G165" s="3" t="inlineStr">
+      <c r="G166" s="3" t="inlineStr">
         <is>
           <t>Trading_$</t>
         </is>
       </c>
-      <c r="H165" s="3" t="inlineStr">
+      <c r="H166" s="3" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="I165" s="3" t="inlineStr">
+      <c r="I166" s="3" t="inlineStr">
         <is>
           <t>also_in (other theses)</t>
         </is>
       </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>NOK</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>NOKIA CORP</t>
-        </is>
-      </c>
-      <c r="C166" s="4" t="n">
-        <v>33531655</v>
-      </c>
-      <c r="D166" s="5" t="n">
-        <v>0.005176089881892354</v>
-      </c>
-      <c r="E166" s="18" t="n">
-        <v>0.0003145970834849382</v>
-      </c>
-      <c r="F166" s="7" t="n">
-        <v>13576801</v>
-      </c>
-      <c r="G166" s="7" t="n">
-        <v>571399</v>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SATS</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr"/>
+          <t>NTRA</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>NATERA INC</t>
+        </is>
+      </c>
       <c r="C167" s="4" t="n">
-        <v>0</v>
+        <v>28335308</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>0</v>
+        <v>0.004893114275227872</v>
       </c>
       <c r="E167" s="18" t="n">
-        <v>-0.02853099709658855</v>
-      </c>
-      <c r="F167" s="6" t="n">
-        <v>-117110506</v>
-      </c>
-      <c r="G167" s="6" t="n">
-        <v>-117110506</v>
+        <v>0.004893114275227872</v>
+      </c>
+      <c r="F167" s="7" t="n">
+        <v>28335308</v>
+      </c>
+      <c r="G167" s="7" t="n">
+        <v>28335308</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="23" t="inlineStr">
         <is>
-          <t>Healthcare/Diagnostics   —   wt 0.4% (Q1 0.0%, Δ +0.4pp) · 1 held</t>
+          <t>AdTech / digital advertising   —   wt 0.1% (Q1 0.1%, Δ +0.0pp) · 1 held</t>
         </is>
       </c>
       <c r="B169" s="24" t="n"/>
@@ -29065,32 +28997,32 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>TABOOLA.COM LTD</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>NATERA INC</t>
+          <t>TABOOLA.COM LTD</t>
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>28335308</v>
+        <v>4175130</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>0.004373959503015985</v>
+        <v>0.0007209869821754592</v>
       </c>
       <c r="E171" s="18" t="n">
-        <v>0.004373959503015985</v>
+        <v>0.0001010913195834644</v>
       </c>
       <c r="F171" s="7" t="n">
-        <v>28335308</v>
+        <v>1630659</v>
       </c>
       <c r="G171" s="7" t="n">
-        <v>28335308</v>
+        <v>71145</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -29098,7 +29030,7 @@
     <row r="173">
       <c r="A173" s="23" t="inlineStr">
         <is>
-          <t>AdTech / digital advertising   —   wt 0.1% (Q1 0.1%, Δ +0.0pp) · 1 held</t>
+          <t>Quantum Computing   —   wt 0.1% (Q1 0.0%, Δ +0.1pp) · 1 held</t>
         </is>
       </c>
       <c r="B173" s="24" t="n"/>
@@ -29160,32 +29092,32 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>TABOOLA.COM LTD</t>
+          <t>QNT</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>TABOOLA.COM LTD</t>
+          <t>QUANTINUUM INC</t>
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>4175130</v>
+        <v>3257584</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>0.0006444909488835318</v>
+        <v>0.0005625395274741292</v>
       </c>
       <c r="E175" s="18" t="n">
-        <v>2.459528629153711e-05</v>
+        <v>0.0005625395274741292</v>
       </c>
       <c r="F175" s="7" t="n">
-        <v>1630659</v>
+        <v>3257584</v>
       </c>
       <c r="G175" s="7" t="n">
-        <v>71145</v>
+        <v>3257584</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -29193,7 +29125,7 @@
     <row r="177">
       <c r="A177" s="23" t="inlineStr">
         <is>
-          <t>Quantum Computing   —   wt 0.1% (Q1 0.0%, Δ +0.1pp) · 1 held</t>
+          <t>Crypto   —   wt 0.0% (Q1 0.0%, Δ -0.0pp) · 1 held</t>
         </is>
       </c>
       <c r="B177" s="24" t="n"/>
@@ -29255,32 +29187,32 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>QNT</t>
+          <t>BTGO</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>QUANTINUUM INC</t>
+          <t>BITGO HOLDINGS INC</t>
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>3257584</v>
+        <v>153385</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>0.000502854618473631</v>
+        <v>2.648745985418006e-05</v>
       </c>
       <c r="E179" s="18" t="n">
-        <v>0.000502854618473631</v>
-      </c>
-      <c r="F179" s="7" t="n">
-        <v>3257584</v>
+        <v>-3.187085777200297e-05</v>
+      </c>
+      <c r="F179" s="6" t="n">
+        <v>-86157</v>
       </c>
       <c r="G179" s="7" t="n">
-        <v>3257584</v>
+        <v>2616</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -29288,7 +29220,7 @@
     <row r="181">
       <c r="A181" s="23" t="inlineStr">
         <is>
-          <t>Crypto   —   wt 0.0% (Q1 0.0%, Δ -0.0pp) · 1 held</t>
+          <t>Defense   —   wt 0.0% (Q1 0.7%, Δ -0.7pp) · 0 held · 1 exited</t>
         </is>
       </c>
       <c r="B181" s="24" t="n"/>
@@ -29350,40 +29282,35 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>BTGO</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>BITGO HOLDINGS INC</t>
-        </is>
-      </c>
+          <t>AVAV</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
       <c r="C183" s="4" t="n">
-        <v>153385</v>
+        <v>0</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>2.367716554801899e-05</v>
+        <v>0</v>
       </c>
       <c r="E183" s="18" t="n">
-        <v>-3.468115207816405e-05</v>
+        <v>-0.007209974000570652</v>
       </c>
       <c r="F183" s="6" t="n">
-        <v>-86157</v>
-      </c>
-      <c r="G183" s="7" t="n">
-        <v>2616</v>
+        <v>-29594609</v>
+      </c>
+      <c r="G183" s="6" t="n">
+        <v>-29594609</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="23" t="inlineStr">
         <is>
-          <t>Defense   —   wt 0.0% (Q1 0.7%, Δ -0.7pp) · 0 held · 1 exited</t>
+          <t>Defense/Security   —   wt 0.0% (Q1 1.1%, Δ -1.1pp) · 0 held · 1 exited</t>
         </is>
       </c>
       <c r="B185" s="24" t="n"/>
@@ -29445,7 +29372,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>AXON</t>
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
@@ -29456,13 +29383,13 @@
         <v>0</v>
       </c>
       <c r="E187" s="18" t="n">
-        <v>-0.007209974000570652</v>
+        <v>-0.01056325113664677</v>
       </c>
       <c r="F187" s="6" t="n">
-        <v>-29594609</v>
+        <v>-43358726</v>
       </c>
       <c r="G187" s="6" t="n">
-        <v>-29594609</v>
+        <v>-43358726</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -29473,7 +29400,7 @@
     <row r="189">
       <c r="A189" s="23" t="inlineStr">
         <is>
-          <t>Defense/Security   —   wt 0.0% (Q1 1.1%, Δ -1.1pp) · 0 held · 1 exited</t>
+          <t>Gaming/Metaverse   —   wt 0.0% (Q1 1.9%, Δ -1.9pp) · 0 held · 1 exited</t>
         </is>
       </c>
       <c r="B189" s="24" t="n"/>
@@ -29535,7 +29462,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>AXON</t>
+          <t>RBLX</t>
         </is>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -29546,13 +29473,13 @@
         <v>0</v>
       </c>
       <c r="E191" s="18" t="n">
-        <v>-0.01056325113664677</v>
+        <v>-0.01906660534174885</v>
       </c>
       <c r="F191" s="6" t="n">
-        <v>-43358726</v>
+        <v>-78262242</v>
       </c>
       <c r="G191" s="6" t="n">
-        <v>-43358726</v>
+        <v>-78262242</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -29563,7 +29490,7 @@
     <row r="193">
       <c r="A193" s="23" t="inlineStr">
         <is>
-          <t>Gaming/Metaverse   —   wt 0.0% (Q1 1.9%, Δ -1.9pp) · 0 held · 1 exited</t>
+          <t>AI/Data Infrastructure   —   wt 0.0% (Q1 0.5%, Δ -0.5pp) · 0 held · 1 exited</t>
         </is>
       </c>
       <c r="B193" s="24" t="n"/>
@@ -29625,7 +29552,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>RBLX</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B195" t="inlineStr"/>
@@ -29636,105 +29563,15 @@
         <v>0</v>
       </c>
       <c r="E195" s="18" t="n">
-        <v>-0.01906660534174885</v>
+        <v>-0.005321114188220493</v>
       </c>
       <c r="F195" s="6" t="n">
-        <v>-78262242</v>
+        <v>-21841451</v>
       </c>
       <c r="G195" s="6" t="n">
-        <v>-78262242</v>
+        <v>-21841451</v>
       </c>
       <c r="H195" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="23" t="inlineStr">
-        <is>
-          <t>AI/Data Infrastructure   —   wt 0.0% (Q1 0.5%, Δ -0.5pp) · 0 held · 1 exited</t>
-        </is>
-      </c>
-      <c r="B197" s="24" t="n"/>
-      <c r="C197" s="24" t="n"/>
-      <c r="D197" s="24" t="n"/>
-      <c r="E197" s="24" t="n"/>
-      <c r="F197" s="24" t="n"/>
-      <c r="G197" s="24" t="n"/>
-      <c r="H197" s="24" t="n"/>
-      <c r="I197" s="24" t="n"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="3" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B198" s="3" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="C198" s="3" t="inlineStr">
-        <is>
-          <t>market_value</t>
-        </is>
-      </c>
-      <c r="D198" s="3" t="inlineStr">
-        <is>
-          <t>wt_eq%</t>
-        </is>
-      </c>
-      <c r="E198" s="3" t="inlineStr">
-        <is>
-          <t>Δwt_pp</t>
-        </is>
-      </c>
-      <c r="F198" s="3" t="inlineStr">
-        <is>
-          <t>value_Δ$</t>
-        </is>
-      </c>
-      <c r="G198" s="3" t="inlineStr">
-        <is>
-          <t>Trading_$</t>
-        </is>
-      </c>
-      <c r="H198" s="3" t="inlineStr">
-        <is>
-          <t>change</t>
-        </is>
-      </c>
-      <c r="I198" s="3" t="inlineStr">
-        <is>
-          <t>also_in (other theses)</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>SNOW</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr"/>
-      <c r="C199" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D199" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E199" s="18" t="n">
-        <v>-0.005321114188220493</v>
-      </c>
-      <c r="F199" s="6" t="n">
-        <v>-21841451</v>
-      </c>
-      <c r="G199" s="6" t="n">
-        <v>-21841451</v>
-      </c>
-      <c r="H199" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
@@ -29815,29 +29652,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI/Datacenter Chips</t>
+          <t>Hyperscalers (quasi-index)</t>
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>687329006</v>
-      </c>
-      <c r="C2" s="20" t="n">
-        <v>0</v>
+        <v>206859970</v>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>67419706</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>687329006</v>
-      </c>
-      <c r="E2" s="20" t="n">
-        <v>0</v>
+        <v>230706198</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>-23846228</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-27 · high_conviction</t>
+          <t>2026-08-14 · moderate</t>
         </is>
       </c>
       <c r="G2" s="26" t="inlineStr">
         <is>
-          <t>Disaggregation of inference into prefill and decode phases will extend the useful life of older Nvidia GPUs (H100s, A100s) by 7-12 years</t>
+          <t>Amazon's DSP model creates political/regulatory risk that Amazon should proactively address — long-term shareholder view</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -29850,29 +29687,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hyperscalers (quasi-index)</t>
+          <t>Neoclouds as durable model</t>
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>206859970</v>
+        <v>131118329</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>67419706</v>
+        <v>28762061</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>230706198</v>
-      </c>
-      <c r="E3" s="6" t="n">
-        <v>-23846228</v>
+        <v>131118329</v>
+      </c>
+      <c r="E3" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-14 · moderate</t>
+          <t>2026-08-14 · high_conviction</t>
         </is>
       </c>
       <c r="G3" s="26" t="inlineStr">
         <is>
-          <t>Amazon's DSP model creates political/regulatory risk that Amazon should proactively address — long-term shareholder view</t>
+          <t>GPU compute has a much longer useful life than bears assume — Ampere GPUs from 2020 are being rented profitably through 2029, implying 9-year asset lives</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -29885,34 +29722,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Neoclouds as durable model</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>131118329</v>
+        <v>79735588</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>28762061</v>
+        <v>101516718</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>131118329</v>
-      </c>
-      <c r="E4" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-08-14 · high_conviction</t>
-        </is>
-      </c>
-      <c r="G4" s="26" t="inlineStr">
-        <is>
-          <t>GPU compute has a much longer useful life than bears assume — Ampere GPUs from 2020 are being rented profitably through 2029, implying 9-year asset lives</t>
-        </is>
+        <v>107474840</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>-27739252</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ALIGNS</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -29920,20 +29747,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Industrial IoT</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>79735588</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>101516718</v>
+        <v>74869487</v>
+      </c>
+      <c r="C5" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>107474840</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>-27739252</v>
+        <v>74869487</v>
+      </c>
+      <c r="E5" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -29945,17 +29772,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Industrial IoT</t>
+          <t>Web / SMB SaaS</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>74869487</v>
-      </c>
-      <c r="C6" s="20" t="n">
-        <v>0</v>
+        <v>36660956</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>-29073506</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>74869487</v>
+        <v>36660956</v>
       </c>
       <c r="E6" s="20" t="n">
         <v>0</v>
@@ -29970,24 +29797,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Web / SMB SaaS</t>
+          <t>AI/Edge Computing</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>36660956</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>-29073506</v>
+        <v>29763477</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>102548865</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>36660956</v>
+        <v>29763477</v>
       </c>
       <c r="E7" s="20" t="n">
         <v>0</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-06-15 · moderate</t>
+        </is>
+      </c>
+      <c r="G7" s="26" t="inlineStr">
+        <is>
+          <t>CDNs like Cloudflare are partially in the token path but currently deliver less than 1% (possibly &lt;10bps) of global tokens consumed</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ALIGNS</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -29995,34 +29832,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI/Edge Computing</t>
+          <t>Healthcare/Diagnostics</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>29763477</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>102548865</v>
+        <v>28335308</v>
+      </c>
+      <c r="C8" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>29763477</v>
+        <v>28335308</v>
       </c>
       <c r="E8" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-06-15 · moderate</t>
-        </is>
-      </c>
-      <c r="G8" s="26" t="inlineStr">
-        <is>
-          <t>CDNs like Cloudflare are partially in the token path but currently deliver less than 1% (possibly &lt;10bps) of global tokens consumed</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ALIGNS</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -30030,24 +29857,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Healthcare/Diagnostics</t>
+          <t>AI/Datacenter Power</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>28335308</v>
+        <v>23208000</v>
       </c>
       <c r="C9" s="20" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>28335308</v>
-      </c>
-      <c r="E9" s="20" t="n">
-        <v>0</v>
+        <v>101949050</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-78741050</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-22 · moderate</t>
+        </is>
+      </c>
+      <c r="G9" s="26" t="inlineStr">
+        <is>
+          <t>IPPs (independent power producers) are reasonably valued within the AI power theme, unlike power equipment, cooling, and optical names which may be overvalued</t>
+        </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ALIGNS</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -30055,34 +29892,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI/Datacenter Power</t>
+          <t>Quantum Computing</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>23208000</v>
+        <v>3257584</v>
       </c>
       <c r="C10" s="20" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>101949050</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>-78741050</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-05-22 · moderate</t>
-        </is>
-      </c>
-      <c r="G10" s="26" t="inlineStr">
-        <is>
-          <t>IPPs (independent power producers) are reasonably valued within the AI power theme, unlike power equipment, cooling, and optical names which may be overvalued</t>
-        </is>
+        <v>3257584</v>
+      </c>
+      <c r="E10" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ALIGNS</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -30090,24 +29917,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Quantum Computing</t>
+          <t>Humanoid robotics / Tesla Optimus</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>3257584</v>
-      </c>
-      <c r="C11" s="20" t="n">
-        <v>0</v>
+        <v>1463688</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>9808836</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>3257584</v>
+        <v>1463688</v>
       </c>
       <c r="E11" s="20" t="n">
         <v>0</v>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-14 · moderate</t>
+        </is>
+      </c>
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t>Robotics will be a major real-world deployment wave, dominated by Tesla vs. Chinese competitors, mirroring the EV competitive dynamic.</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -30115,34 +29952,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Humanoid robotics / Tesla Optimus</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>1463688</v>
+        <v>1188896</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>9808836</v>
+        <v>27921230</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>1463688</v>
+        <v>1188896</v>
       </c>
       <c r="E12" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-07-14 · moderate</t>
-        </is>
-      </c>
-      <c r="G12" s="26" t="inlineStr">
-        <is>
-          <t>Robotics will be a major real-world deployment wave, dominated by Tesla vs. Chinese competitors, mirroring the EV competitive dynamic.</t>
-        </is>
-      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -30150,20 +29977,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Payments</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>1188896</v>
+        <v>958464</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>27921230</v>
+        <v>691479</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1188896</v>
-      </c>
-      <c r="E13" s="20" t="n">
-        <v>0</v>
+        <v>22611240</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-21652776</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -30175,20 +30002,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Payments</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>958464</v>
+        <v>405953</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>691479</v>
+        <v>444129</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>22611240</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>-21652776</v>
+        <v>405953</v>
+      </c>
+      <c r="E14" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -30200,24 +30027,34 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Nvidia GPU moat / CUDA ecosystem</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>405953</v>
+        <v>139863</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>444129</v>
+        <v>32076328</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>405953</v>
+        <v>139863</v>
       </c>
       <c r="E15" s="20" t="n">
         <v>0</v>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-14 · high_conviction</t>
+        </is>
+      </c>
+      <c r="G15" s="26" t="inlineStr">
+        <is>
+          <t>Anthropic S1 will be the most important demand signal for the entire AI infrastructure food chain</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -30225,34 +30062,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nvidia GPU moat / CUDA ecosystem</t>
+          <t>AdTech / digital advertising</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>139863</v>
+        <v>71145</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>32076328</v>
+        <v>1559514</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>139863</v>
+        <v>71145</v>
       </c>
       <c r="E16" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-08-14 · high_conviction</t>
-        </is>
-      </c>
-      <c r="G16" s="26" t="inlineStr">
-        <is>
-          <t>Anthropic S1 will be the most important demand signal for the entire AI infrastructure food chain</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -30260,17 +30087,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AdTech / digital advertising</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>71145</v>
-      </c>
-      <c r="C17" s="7" t="n">
-        <v>1559514</v>
+        <v>2616</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>-88773</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>71145</v>
+        <v>2616</v>
       </c>
       <c r="E17" s="20" t="n">
         <v>0</v>
@@ -30285,17 +30112,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Crypto</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n">
-        <v>2616</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>-88773</v>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>2616</v>
+          <t>Orbital / space-based compute</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="E18" s="20" t="n">
         <v>0</v>
@@ -30310,7 +30137,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Orbital / space-based compute</t>
+          <t>AI/Datacenter Chips</t>
         </is>
       </c>
       <c r="B19" s="20" t="n">
@@ -30325,9 +30152,19 @@
       <c r="E19" s="20" t="n">
         <v>0</v>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-27 · high_conviction</t>
+        </is>
+      </c>
+      <c r="G19" s="26" t="inlineStr">
+        <is>
+          <t>Disaggregation of inference into prefill and decode phases will extend the useful life of older Nvidia GPUs (H100s, A100s) by 7-12 years</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -30937,7 +30774,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>IPO_RECLASSIFICATION</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -31010,7 +30847,7 @@
     <row r="2">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>NEW positions (genuine buys) — 12</t>
+          <t>NEW positions (genuine buys) — 11</t>
         </is>
       </c>
       <c r="B2" s="24" t="n"/>
@@ -31022,23 +30859,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CBRS</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CEREBRAS SYSTEMS INC</t>
+          <t>META PLATFORMS INC</t>
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>687329006</v>
+        <v>226876313</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>0.1060990491965794</v>
+        <v>0.03917838923266219</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI/Datacenter Chips</t>
+          <t>Hyperscalers (quasi-index)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -31050,23 +30887,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>META PLATFORMS INC</t>
+          <t>AMPHENOL CORP</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>226876313</v>
+        <v>112856966</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.03502159938602323</v>
+        <v>0.01948883108641369</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hyperscalers (quasi-index)</t>
+          <t>AI/Datacenter Networking</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -31078,155 +30915,151 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>GTLB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AMPHENOL CORP</t>
+          <t>GITLAB INC</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>112856966</v>
+        <v>102982850</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.01742108463819246</v>
+        <v>0.01778370834856112</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI/Datacenter Networking</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
+          <t>Enterprise SaaS</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>CIFR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GITLAB INC</t>
+          <t>CIPHER DIGITAL INC</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>102982850</v>
+        <v>87867021</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.01589687380158951</v>
+        <v>0.01517341455320857</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Enterprise SaaS</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>AI/Datacenter Power</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CIFR</t>
+          <t>IOT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CIPHER DIGITAL INC</t>
+          <t>SAMSARA INC</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>87867021</v>
+        <v>74869487</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.0135635296960476</v>
+        <v>0.01292892089327872</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI/Datacenter Power</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
+          <t>Industrial IoT</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IOT</t>
+          <t>PDFS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SAMSARA INC</t>
+          <t>PDF SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>74869487</v>
+        <v>46617763</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.01155717467936405</v>
+        <v>0.00805024041434417</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Industrial IoT</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>Semiconductor Supply Chain</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PDFS</t>
+          <t>TTAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PDF SOLUTIONS INC</t>
+          <t>SERVICETITAN INC</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>46617763</v>
+        <v>38331325</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.007196117560578376</v>
+        <v>0.006619287623268433</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Semiconductor Supply Chain</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
+          <t>Enterprise SaaS</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TTAN</t>
+          <t>NTRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SERVICETITAN INC</t>
+          <t>NATERA INC</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>38331325</v>
+        <v>28335308</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.005916987500080966</v>
+        <v>0.004893114275227872</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Enterprise SaaS</t>
+          <t>Healthcare/Diagnostics</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -31234,23 +31067,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>N52A8C105</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NATERA INC</t>
+          <t>INNIO NV</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>28335308</v>
+        <v>13790927</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.004373959503015985</v>
+        <v>0.002381501615310675</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Healthcare/Diagnostics</t>
+          <t>AI/Datacenter Power</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -31258,23 +31091,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N52A8C105</t>
+          <t>QNT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INNIO NV</t>
+          <t>QUANTINUUM INC</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>13790927</v>
+        <v>3257584</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.002128826558266094</v>
+        <v>0.0005625395274741292</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI/Datacenter Power</t>
+          <t>Quantum Computing</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -31282,90 +31115,94 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>QNT</t>
+          <t>FRVO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>QUANTINUUM INC</t>
+          <t>FERVO ENERGY CO</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3257584</v>
+        <v>291102</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.000502854618473631</v>
+        <v>5.026927364782426e-05</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Quantum Computing</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>FRVO</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>FERVO ENERGY CO</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>291102</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>4.493575150998744e-05</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
           <t>AI/Datacenter Power</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>IPO reclassification — 2 (entered the 13F at IPO, NOT a Q2 buy)</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="n"/>
+      <c r="C15" s="24" t="n"/>
+      <c r="D15" s="24" t="n"/>
+      <c r="E15" s="24" t="n"/>
+      <c r="F15" s="24" t="n"/>
+    </row>
     <row r="16">
-      <c r="A16" s="23" t="inlineStr">
-        <is>
-          <t>IPO reclassification — 1 (entered the 13F at IPO, NOT a Q2 buy)</t>
-        </is>
-      </c>
-      <c r="B16" s="24" t="n"/>
-      <c r="C16" s="24" t="n"/>
-      <c r="D16" s="24" t="n"/>
-      <c r="E16" s="24" t="n"/>
-      <c r="F16" s="24" t="n"/>
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>SPCX</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>SPACE EXPLORATION TECHN CORP</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>4670106641</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.4189079214879446</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Orbital / space-based compute</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>SPCX</t>
+          <t>CBRS</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>SPACE EXPLORATION TECHN CORP</t>
+          <t>CEREBRAS SYSTEMS INC</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>4670106641</v>
+        <v>687329006</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.4189079214879446</v>
+        <v>0.06165331702579317</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orbital / space-based compute</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
+          <t>AI/Datacenter Chips</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="23" t="inlineStr">
